--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1cfefa7afb5b64df/bsbox/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="228" documentId="13_ncr:1_{54C4E61B-1CE2-4548-BDA4-A6B0798C7B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{960CEF64-E51F-4B59-89C2-94C67AE28539}"/>
+  <xr:revisionPtr revIDLastSave="255" documentId="13_ncr:1_{54C4E61B-1CE2-4548-BDA4-A6B0798C7B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EFAD67A-35B5-48D6-B441-AC2F04256476}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -1405,21 +1405,20 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="47" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="47" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1783,250 +1782,250 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:J137"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="74.5703125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="74.5703125" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <v>15.8</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <v>16.899999999999999</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <v>15.8</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <v>16.899999999999999</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>15.8</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>16.899999999999999</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>171</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>15.8</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <v>16.899999999999999</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>15.8</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <v>16.899999999999999</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <v>15.8</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <v>16.899999999999999</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <v>15.8</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <v>16.899999999999999</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2">
         <v>15.8</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <v>16.899999999999999</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="2">
         <v>15.8</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="2">
         <v>16.899999999999999</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>105</v>
       </c>
@@ -2039,17 +2038,17 @@
       <c r="D11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="4">
         <v>5.99</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <v>5.99</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>106</v>
       </c>
@@ -2062,17 +2061,17 @@
       <c r="D12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <v>5.99</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="2">
         <v>5.99</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>107</v>
       </c>
@@ -2085,17 +2084,17 @@
       <c r="D13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="4">
         <v>5.99</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="2">
         <v>5.99</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>108</v>
       </c>
@@ -2108,17 +2107,17 @@
       <c r="D14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="4">
         <v>5.99</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="2">
         <v>5.99</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>109</v>
       </c>
@@ -2131,17 +2130,17 @@
       <c r="D15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="4">
         <v>5.99</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="2">
         <v>5.99</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>110</v>
       </c>
@@ -2154,17 +2153,17 @@
       <c r="D16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="4">
         <v>5.99</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="2">
         <v>5.99</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>111</v>
       </c>
@@ -2177,17 +2176,17 @@
       <c r="D17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="4">
         <v>5.99</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="2">
         <v>5.99</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>112</v>
       </c>
@@ -2200,17 +2199,17 @@
       <c r="D18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="4">
         <v>5.99</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="2">
         <v>5.99</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>113</v>
       </c>
@@ -2223,17 +2222,17 @@
       <c r="D19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="4">
         <v>3.5</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="2">
         <v>84</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G19" s="5">
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>114</v>
       </c>
@@ -2246,17 +2245,17 @@
       <c r="D20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="4">
         <v>3.5</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="2">
         <v>84</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G20" s="5">
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>134</v>
       </c>
@@ -2269,18 +2268,18 @@
       <c r="D21" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="4">
         <v>1.99</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="2">
         <f>E21*24</f>
         <v>47.76</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G21" s="5">
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>137</v>
       </c>
@@ -2293,18 +2292,18 @@
       <c r="D22" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="4">
         <v>1.99</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="2">
         <f t="shared" ref="F22:F26" si="0">E22*24</f>
         <v>47.76</v>
       </c>
-      <c r="G22" s="6">
+      <c r="G22" s="5">
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>138</v>
       </c>
@@ -2317,18 +2316,18 @@
       <c r="D23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="4">
         <v>1.99</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="2">
         <f t="shared" si="0"/>
         <v>47.76</v>
       </c>
-      <c r="G23" s="6">
+      <c r="G23" s="5">
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>141</v>
       </c>
@@ -2341,18 +2340,18 @@
       <c r="D24" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="4">
         <v>1.99</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="2">
         <f t="shared" si="0"/>
         <v>47.76</v>
       </c>
-      <c r="G24" s="6">
+      <c r="G24" s="5">
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>142</v>
       </c>
@@ -2365,18 +2364,18 @@
       <c r="D25" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="4">
         <v>1.99</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="2">
         <f t="shared" si="0"/>
         <v>47.76</v>
       </c>
-      <c r="G25" s="6">
+      <c r="G25" s="5">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>144</v>
       </c>
@@ -2389,18 +2388,18 @@
       <c r="D26" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="4">
         <v>1.99</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="2">
         <f t="shared" si="0"/>
         <v>47.76</v>
       </c>
-      <c r="G26" s="6">
+      <c r="G26" s="5">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>29</v>
       </c>
@@ -2413,17 +2412,17 @@
       <c r="D27" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="4">
         <v>6.94</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="2">
         <v>83.28</v>
       </c>
-      <c r="G27" s="6">
+      <c r="G27" s="5">
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>30</v>
       </c>
@@ -2436,17 +2435,17 @@
       <c r="D28" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28" s="4">
         <v>6.94</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="2">
         <v>83.28</v>
       </c>
-      <c r="G28" s="6">
+      <c r="G28" s="5">
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>31</v>
       </c>
@@ -2459,17 +2458,17 @@
       <c r="D29" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E29" s="4">
         <v>3.96</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="2">
         <v>118.8</v>
       </c>
-      <c r="G29" s="6">
+      <c r="G29" s="5">
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>32</v>
       </c>
@@ -2482,17 +2481,17 @@
       <c r="D30" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E30" s="4">
         <v>0.84</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F30" s="2">
         <v>26.64</v>
       </c>
-      <c r="G30" s="6">
+      <c r="G30" s="5">
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>33</v>
       </c>
@@ -2505,17 +2504,17 @@
       <c r="D31" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E31" s="5">
+      <c r="E31" s="4">
         <v>0.93</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F31" s="2">
         <v>29.8</v>
       </c>
-      <c r="G31" s="6">
+      <c r="G31" s="5">
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>34</v>
       </c>
@@ -2528,17 +2527,17 @@
       <c r="D32" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E32" s="4">
         <v>12.99</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="2">
         <v>12.99</v>
       </c>
-      <c r="G32" s="6">
+      <c r="G32" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>35</v>
       </c>
@@ -2551,17 +2550,17 @@
       <c r="D33" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E33" s="4">
         <v>12.99</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33" s="2">
         <v>12.99</v>
       </c>
-      <c r="G33" s="6">
+      <c r="G33" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>36</v>
       </c>
@@ -2574,17 +2573,17 @@
       <c r="D34" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E34" s="4">
         <v>12.99</v>
       </c>
-      <c r="F34" s="3">
+      <c r="F34" s="2">
         <v>12.99</v>
       </c>
-      <c r="G34" s="6">
+      <c r="G34" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>37</v>
       </c>
@@ -2597,17 +2596,17 @@
       <c r="D35" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E35" s="4">
         <v>0.41</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F35" s="2">
         <v>25.58</v>
       </c>
-      <c r="G35" s="6">
+      <c r="G35" s="5">
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>38</v>
       </c>
@@ -2620,17 +2619,17 @@
       <c r="D36" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E36" s="4">
         <v>0.43</v>
       </c>
-      <c r="F36" s="3">
+      <c r="F36" s="2">
         <v>23.85</v>
       </c>
-      <c r="G36" s="6">
+      <c r="G36" s="5">
         <v>56</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>39</v>
       </c>
@@ -2643,17 +2642,17 @@
       <c r="D37" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E37" s="5">
+      <c r="E37" s="4">
         <v>3.82</v>
       </c>
-      <c r="F37" s="3">
+      <c r="F37" s="2">
         <v>61.12</v>
       </c>
-      <c r="G37" s="6">
+      <c r="G37" s="5">
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>40</v>
       </c>
@@ -2666,17 +2665,17 @@
       <c r="D38" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E38" s="5">
+      <c r="E38" s="4">
         <v>3.82</v>
       </c>
-      <c r="F38" s="3">
+      <c r="F38" s="2">
         <v>61.12</v>
       </c>
-      <c r="G38" s="6">
+      <c r="G38" s="5">
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>41</v>
       </c>
@@ -2689,17 +2688,17 @@
       <c r="D39" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E39" s="5">
+      <c r="E39" s="4">
         <v>3.82</v>
       </c>
-      <c r="F39" s="3">
+      <c r="F39" s="2">
         <v>61.12</v>
       </c>
-      <c r="G39" s="6">
+      <c r="G39" s="5">
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>42</v>
       </c>
@@ -2712,17 +2711,17 @@
       <c r="D40" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E40" s="5">
+      <c r="E40" s="4">
         <v>0.61</v>
       </c>
-      <c r="F40" s="3">
+      <c r="F40" s="2">
         <v>25.68</v>
       </c>
-      <c r="G40" s="6">
+      <c r="G40" s="5">
         <v>42</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>43</v>
       </c>
@@ -2735,17 +2734,17 @@
       <c r="D41" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E41" s="5">
+      <c r="E41" s="4">
         <v>0.61</v>
       </c>
-      <c r="F41" s="3">
+      <c r="F41" s="2">
         <v>25.68</v>
       </c>
-      <c r="G41" s="6">
+      <c r="G41" s="5">
         <v>42</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>44</v>
       </c>
@@ -2758,17 +2757,17 @@
       <c r="D42" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E42" s="5">
+      <c r="E42" s="4">
         <v>0.61</v>
       </c>
-      <c r="F42" s="3">
+      <c r="F42" s="2">
         <v>25.68</v>
       </c>
-      <c r="G42" s="6">
+      <c r="G42" s="5">
         <v>42</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>45</v>
       </c>
@@ -2781,17 +2780,17 @@
       <c r="D43" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E43" s="5">
+      <c r="E43" s="4">
         <v>1.58</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43" s="2">
         <v>38.15</v>
       </c>
-      <c r="G43" s="6">
+      <c r="G43" s="5">
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>46</v>
       </c>
@@ -2804,17 +2803,17 @@
       <c r="D44" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E44" s="5">
+      <c r="E44" s="4">
         <v>6.94</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="2">
         <v>173.5</v>
       </c>
-      <c r="G44" s="6">
+      <c r="G44" s="5">
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>47</v>
       </c>
@@ -2827,17 +2826,17 @@
       <c r="D45" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E45" s="5">
+      <c r="E45" s="4">
         <v>0.59</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="2">
         <v>35.76</v>
       </c>
-      <c r="G45" s="6">
+      <c r="G45" s="5">
         <v>60</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>48</v>
       </c>
@@ -2850,17 +2849,17 @@
       <c r="D46" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E46" s="5">
+      <c r="E46" s="4">
         <v>13.68</v>
       </c>
-      <c r="F46" s="3">
+      <c r="F46" s="2">
         <v>164.16</v>
       </c>
-      <c r="G46" s="6">
+      <c r="G46" s="5">
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>49</v>
       </c>
@@ -2873,13 +2872,13 @@
       <c r="D47" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E47" s="5">
+      <c r="E47" s="4">
         <v>15.13</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="2">
         <v>181.56</v>
       </c>
-      <c r="G47" s="6">
+      <c r="G47" s="5">
         <v>12</v>
       </c>
     </row>
@@ -2896,13 +2895,13 @@
       <c r="D48" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E48" s="5">
+      <c r="E48" s="4">
         <v>2.0570000000000004</v>
       </c>
-      <c r="F48" s="3">
+      <c r="F48" s="2">
         <v>61.600000000000009</v>
       </c>
-      <c r="G48" s="6">
+      <c r="G48" s="5">
         <v>30</v>
       </c>
     </row>
@@ -2919,13 +2918,13 @@
       <c r="D49" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E49" s="5">
+      <c r="E49" s="4">
         <v>5.2250000000000005</v>
       </c>
-      <c r="F49" s="3">
+      <c r="F49" s="2">
         <v>104.50000000000001</v>
       </c>
-      <c r="G49" s="6">
+      <c r="G49" s="5">
         <v>20</v>
       </c>
     </row>
@@ -2942,13 +2941,13 @@
       <c r="D50" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E50" s="5">
+      <c r="E50" s="4">
         <v>2.2000000000000002</v>
       </c>
-      <c r="F50" s="3">
+      <c r="F50" s="2">
         <v>48.400000000000006</v>
       </c>
-      <c r="G50" s="6">
+      <c r="G50" s="5">
         <v>22</v>
       </c>
     </row>
@@ -2965,13 +2964,13 @@
       <c r="D51" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E51" s="5">
+      <c r="E51" s="4">
         <v>2.2000000000000002</v>
       </c>
-      <c r="F51" s="3">
+      <c r="F51" s="2">
         <v>48.400000000000006</v>
       </c>
-      <c r="G51" s="6">
+      <c r="G51" s="5">
         <v>22</v>
       </c>
     </row>
@@ -2988,13 +2987,13 @@
       <c r="D52" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E52" s="5">
+      <c r="E52" s="4">
         <v>2.8600000000000003</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F52" s="2">
         <v>57.2</v>
       </c>
-      <c r="G52" s="6">
+      <c r="G52" s="5">
         <v>20</v>
       </c>
     </row>
@@ -3011,13 +3010,13 @@
       <c r="D53" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E53" s="5">
+      <c r="E53" s="4">
         <v>3.08</v>
       </c>
-      <c r="F53" s="3">
+      <c r="F53" s="2">
         <v>61.600000000000009</v>
       </c>
-      <c r="G53" s="6">
+      <c r="G53" s="5">
         <v>20</v>
       </c>
     </row>
@@ -3034,13 +3033,13 @@
       <c r="D54" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E54" s="5">
+      <c r="E54" s="4">
         <v>2.75</v>
       </c>
-      <c r="F54" s="3">
+      <c r="F54" s="2">
         <v>66</v>
       </c>
-      <c r="G54" s="6">
+      <c r="G54" s="5">
         <v>24</v>
       </c>
     </row>
@@ -3057,13 +3056,13 @@
       <c r="D55" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E55" s="5">
+      <c r="E55" s="4">
         <v>4.4000000000000004</v>
       </c>
-      <c r="F55" s="3">
+      <c r="F55" s="2">
         <v>88</v>
       </c>
-      <c r="G55" s="6">
+      <c r="G55" s="5">
         <v>20</v>
       </c>
     </row>
@@ -3080,13 +3079,13 @@
       <c r="D56" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E56" s="5">
+      <c r="E56" s="4">
         <v>2.5739999999999998</v>
       </c>
-      <c r="F56" s="3">
+      <c r="F56" s="2">
         <v>61.600000000000009</v>
       </c>
-      <c r="G56" s="6">
+      <c r="G56" s="5">
         <v>24</v>
       </c>
     </row>
@@ -3103,13 +3102,13 @@
       <c r="D57" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E57" s="5">
+      <c r="E57" s="4">
         <v>2.5739999999999998</v>
       </c>
-      <c r="F57" s="3">
+      <c r="F57" s="2">
         <v>61.600000000000009</v>
       </c>
-      <c r="G57" s="6">
+      <c r="G57" s="5">
         <v>24</v>
       </c>
     </row>
@@ -3126,16 +3125,16 @@
       <c r="D58" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E58" s="5">
+      <c r="E58" s="4">
         <v>2.36</v>
       </c>
-      <c r="F58" s="3">
+      <c r="F58" s="2">
         <v>42.9</v>
       </c>
-      <c r="G58" s="6" t="s">
+      <c r="G58" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="H58" s="2">
+      <c r="H58">
         <f>48.4/50</f>
         <v>0.96799999999999997</v>
       </c>
@@ -3153,13 +3152,13 @@
       <c r="D59" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E59" s="5">
+      <c r="E59" s="4">
         <v>2.75</v>
       </c>
-      <c r="F59" s="3">
+      <c r="F59" s="2">
         <v>82.5</v>
       </c>
-      <c r="G59" s="6">
+      <c r="G59" s="5">
         <v>30</v>
       </c>
     </row>
@@ -3176,13 +3175,13 @@
       <c r="D60" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E60" s="5">
+      <c r="E60" s="4">
         <v>11.43</v>
       </c>
-      <c r="F60" s="3">
+      <c r="F60" s="2">
         <v>14.3</v>
       </c>
-      <c r="G60" s="6">
+      <c r="G60" s="5">
         <v>1</v>
       </c>
     </row>
@@ -3199,13 +3198,13 @@
       <c r="D61" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E61" s="5">
+      <c r="E61" s="4">
         <v>17.62</v>
       </c>
-      <c r="F61" s="3">
+      <c r="F61" s="2">
         <v>225.50000000000003</v>
       </c>
-      <c r="G61" s="6">
+      <c r="G61" s="5">
         <v>15</v>
       </c>
     </row>
@@ -3222,13 +3221,13 @@
       <c r="D62" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E62" s="5">
+      <c r="E62" s="4">
         <v>1.54</v>
       </c>
-      <c r="F62" s="3">
+      <c r="F62" s="2">
         <v>46.2</v>
       </c>
-      <c r="G62" s="6">
+      <c r="G62" s="5">
         <v>30</v>
       </c>
     </row>
@@ -3245,13 +3244,13 @@
       <c r="D63" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E63" s="5">
+      <c r="E63" s="4">
         <v>2.2000000000000002</v>
       </c>
-      <c r="F63" s="3">
+      <c r="F63" s="2">
         <v>48.400000000000006</v>
       </c>
-      <c r="G63" s="6">
+      <c r="G63" s="5">
         <v>22</v>
       </c>
     </row>
@@ -3268,13 +3267,13 @@
       <c r="D64" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E64" s="5">
+      <c r="E64" s="4">
         <v>2.2000000000000002</v>
       </c>
-      <c r="F64" s="3">
+      <c r="F64" s="2">
         <v>48.400000000000006</v>
       </c>
-      <c r="G64" s="6">
+      <c r="G64" s="5">
         <v>22</v>
       </c>
     </row>
@@ -3291,13 +3290,13 @@
       <c r="D65" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E65" s="5">
+      <c r="E65" s="4">
         <v>2.2000000000000002</v>
       </c>
-      <c r="F65" s="3">
+      <c r="F65" s="2">
         <v>48.400000000000006</v>
       </c>
-      <c r="G65" s="6">
+      <c r="G65" s="5">
         <v>22</v>
       </c>
     </row>
@@ -3314,13 +3313,13 @@
       <c r="D66" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E66" s="5">
+      <c r="E66" s="4">
         <v>7.5</v>
       </c>
-      <c r="F66" s="3">
+      <c r="F66" s="2">
         <v>150</v>
       </c>
-      <c r="G66" s="6">
+      <c r="G66" s="5">
         <v>20</v>
       </c>
     </row>
@@ -3337,13 +3336,13 @@
       <c r="D67" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E67" s="5">
+      <c r="E67" s="4">
         <v>4.0369999999999999</v>
       </c>
-      <c r="F67" s="3">
+      <c r="F67" s="2">
         <v>60.500000000000007</v>
       </c>
-      <c r="G67" s="6">
+      <c r="G67" s="5">
         <v>15</v>
       </c>
     </row>
@@ -3360,13 +3359,13 @@
       <c r="D68" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E68" s="5">
+      <c r="E68" s="4">
         <v>5.5</v>
       </c>
-      <c r="F68" s="3">
+      <c r="F68" s="2">
         <v>82.5</v>
       </c>
-      <c r="G68" s="6">
+      <c r="G68" s="5">
         <v>15</v>
       </c>
     </row>
@@ -3383,13 +3382,13 @@
       <c r="D69" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E69" s="5">
+      <c r="E69" s="4">
         <v>3.3880000000000003</v>
       </c>
-      <c r="F69" s="3">
+      <c r="F69" s="2">
         <v>141.9</v>
       </c>
-      <c r="G69" s="6">
+      <c r="G69" s="5">
         <v>42</v>
       </c>
     </row>
@@ -3406,13 +3405,13 @@
       <c r="D70" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E70" s="5">
+      <c r="E70" s="4">
         <v>2.4200000000000004</v>
       </c>
-      <c r="F70" s="3">
+      <c r="F70" s="2">
         <v>48.400000000000006</v>
       </c>
-      <c r="G70" s="6">
+      <c r="G70" s="5">
         <v>20</v>
       </c>
     </row>
@@ -3429,13 +3428,13 @@
       <c r="D71" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E71" s="5">
+      <c r="E71" s="4">
         <v>2.1779999999999999</v>
       </c>
-      <c r="F71" s="3">
+      <c r="F71" s="2">
         <v>91.300000000000011</v>
       </c>
-      <c r="G71" s="6">
+      <c r="G71" s="5">
         <v>42</v>
       </c>
     </row>
@@ -3452,13 +3451,13 @@
       <c r="D72" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E72" s="5">
+      <c r="E72" s="4">
         <v>1.3860000000000001</v>
       </c>
-      <c r="F72" s="3">
+      <c r="F72" s="2">
         <v>48.400000000000006</v>
       </c>
-      <c r="G72" s="6">
+      <c r="G72" s="5">
         <v>35</v>
       </c>
     </row>
@@ -3475,13 +3474,13 @@
       <c r="D73" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E73" s="5">
+      <c r="E73" s="4">
         <v>5.6539999999999999</v>
       </c>
-      <c r="F73" s="3">
+      <c r="F73" s="2">
         <v>84.7</v>
       </c>
-      <c r="G73" s="6">
+      <c r="G73" s="5">
         <v>15</v>
       </c>
     </row>
@@ -3498,13 +3497,13 @@
       <c r="D74" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E74" s="5">
+      <c r="E74" s="4">
         <v>5.6539999999999999</v>
       </c>
-      <c r="F74" s="3">
+      <c r="F74" s="2">
         <v>84.7</v>
       </c>
-      <c r="G74" s="6">
+      <c r="G74" s="5">
         <v>15</v>
       </c>
     </row>
@@ -3521,13 +3520,13 @@
       <c r="D75" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E75" s="5">
+      <c r="E75" s="4">
         <v>5.6539999999999999</v>
       </c>
-      <c r="F75" s="3">
+      <c r="F75" s="2">
         <v>84.7</v>
       </c>
-      <c r="G75" s="6">
+      <c r="G75" s="5">
         <v>15</v>
       </c>
     </row>
@@ -3544,13 +3543,13 @@
       <c r="D76" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E76" s="5">
+      <c r="E76" s="4">
         <v>5.6539999999999999</v>
       </c>
-      <c r="F76" s="3">
+      <c r="F76" s="2">
         <v>84.7</v>
       </c>
-      <c r="G76" s="6">
+      <c r="G76" s="5">
         <v>15</v>
       </c>
     </row>
@@ -3567,16 +3566,16 @@
       <c r="D77" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E77" s="5">
+      <c r="E77" s="4">
         <v>5.6539999999999999</v>
       </c>
-      <c r="F77" s="3">
+      <c r="F77" s="2">
         <v>84.7</v>
       </c>
-      <c r="G77" s="6">
+      <c r="G77" s="5">
         <v>15</v>
       </c>
-      <c r="J77" s="2">
+      <c r="J77">
         <v>50</v>
       </c>
     </row>
@@ -3593,16 +3592,16 @@
       <c r="D78" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E78" s="5">
+      <c r="E78" s="4">
         <v>5.6539999999999999</v>
       </c>
-      <c r="F78" s="3">
+      <c r="F78" s="2">
         <v>84.7</v>
       </c>
-      <c r="G78" s="6">
+      <c r="G78" s="5">
         <v>15</v>
       </c>
-      <c r="J78" s="2">
+      <c r="J78">
         <v>20</v>
       </c>
     </row>
@@ -3619,19 +3618,19 @@
       <c r="D79" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E79" s="5">
+      <c r="E79" s="4">
         <v>5.6539999999999999</v>
       </c>
-      <c r="F79" s="3">
+      <c r="F79" s="2">
         <v>84.7</v>
       </c>
-      <c r="G79" s="6">
+      <c r="G79" s="5">
         <v>15</v>
       </c>
       <c r="H79" s="1">
         <v>112</v>
       </c>
-      <c r="J79" s="2">
+      <c r="J79">
         <v>190</v>
       </c>
     </row>
@@ -3648,20 +3647,20 @@
       <c r="D80" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E80" s="5">
+      <c r="E80" s="4">
         <v>4.6399999999999997</v>
       </c>
-      <c r="F80" s="3">
+      <c r="F80" s="2">
         <v>111.43</v>
       </c>
-      <c r="G80" s="6">
+      <c r="G80" s="5">
         <v>24</v>
       </c>
-      <c r="H80" s="2" t="e">
+      <c r="H80" t="e">
         <f>#REF!*1.5</f>
         <v>#REF!</v>
       </c>
-      <c r="J80" s="2">
+      <c r="J80">
         <v>95</v>
       </c>
     </row>
@@ -3678,16 +3677,16 @@
       <c r="D81" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E81" s="5">
+      <c r="E81" s="4">
         <v>2.14</v>
       </c>
-      <c r="F81" s="3">
+      <c r="F81" s="2">
         <v>64.290000000000006</v>
       </c>
-      <c r="G81" s="6">
+      <c r="G81" s="5">
         <v>30</v>
       </c>
-      <c r="J81" s="2">
+      <c r="J81">
         <v>4</v>
       </c>
     </row>
@@ -3704,16 +3703,16 @@
       <c r="D82" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E82" s="5">
+      <c r="E82" s="4">
         <v>10.450000000000001</v>
       </c>
-      <c r="F82" s="3">
+      <c r="F82" s="2">
         <v>10.450000000000001</v>
       </c>
-      <c r="G82" s="6">
+      <c r="G82" s="5">
         <v>1</v>
       </c>
-      <c r="J82" s="2">
+      <c r="J82">
         <f>SUM(J77:J81)</f>
         <v>359</v>
       </c>
@@ -3731,17 +3730,17 @@
       <c r="D83" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E83" s="5">
+      <c r="E83" s="4">
         <v>2.52</v>
       </c>
-      <c r="F83" s="3">
+      <c r="F83" s="2">
         <v>75.709999999999994</v>
       </c>
-      <c r="G83" s="6">
+      <c r="G83" s="5">
         <v>30</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>129</v>
       </c>
@@ -3754,13 +3753,13 @@
       <c r="D84" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E84" s="5">
-        <v>50</v>
-      </c>
-      <c r="F84" s="3">
-        <v>50</v>
-      </c>
-      <c r="G84" s="6">
+      <c r="E84" s="4">
+        <v>50</v>
+      </c>
+      <c r="F84" s="2">
+        <v>50</v>
+      </c>
+      <c r="G84" s="5">
         <v>6</v>
       </c>
     </row>
@@ -3777,16 +3776,16 @@
       <c r="D85" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E85" s="5">
+      <c r="E85" s="4">
         <v>1.51</v>
       </c>
-      <c r="F85" s="3">
+      <c r="F85" s="2">
         <v>52.65</v>
       </c>
-      <c r="G85" s="6" t="s">
+      <c r="G85" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="J85" s="2">
+      <c r="J85">
         <v>1927.1</v>
       </c>
     </row>
@@ -3803,16 +3802,16 @@
       <c r="D86" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E86" s="3">
+      <c r="E86" s="2">
         <v>2.63</v>
       </c>
-      <c r="F86" s="3">
+      <c r="F86" s="2">
         <v>52.64</v>
       </c>
-      <c r="G86" s="6">
+      <c r="G86" s="5">
         <v>20</v>
       </c>
-      <c r="J86" s="2">
+      <c r="J86">
         <f>J85-J82</f>
         <v>1568.1</v>
       </c>
@@ -3830,13 +3829,13 @@
       <c r="D87" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E87" s="3">
+      <c r="E87" s="2">
         <v>2.63</v>
       </c>
-      <c r="F87" s="3">
+      <c r="F87" s="2">
         <v>52.64</v>
       </c>
-      <c r="G87" s="6">
+      <c r="G87" s="5">
         <v>20</v>
       </c>
     </row>
@@ -3853,13 +3852,13 @@
       <c r="D88" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E88" s="3">
+      <c r="E88" s="2">
         <v>2.63</v>
       </c>
-      <c r="F88" s="3">
+      <c r="F88" s="2">
         <v>52.64</v>
       </c>
-      <c r="G88" s="6">
+      <c r="G88" s="5">
         <v>20</v>
       </c>
     </row>
@@ -3870,19 +3869,19 @@
       <c r="B89" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="C89" t="s">
         <v>204</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E89" s="3">
+      <c r="E89" s="2">
         <v>2.83</v>
       </c>
-      <c r="F89" s="3">
+      <c r="F89" s="2">
         <v>84.7</v>
       </c>
-      <c r="G89" s="6">
+      <c r="G89" s="5">
         <v>30</v>
       </c>
     </row>
@@ -3899,13 +3898,13 @@
       <c r="D90" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E90" s="3">
+      <c r="E90" s="2">
         <v>2.15</v>
       </c>
-      <c r="F90" s="3">
+      <c r="F90" s="2">
         <v>45</v>
       </c>
-      <c r="G90" s="6" t="s">
+      <c r="G90" s="5" t="s">
         <v>154</v>
       </c>
     </row>
@@ -3922,13 +3921,13 @@
       <c r="D91" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E91" s="3">
+      <c r="E91" s="2">
         <v>2.15</v>
       </c>
-      <c r="F91" s="3">
+      <c r="F91" s="2">
         <v>45</v>
       </c>
-      <c r="G91" s="6" t="s">
+      <c r="G91" s="5" t="s">
         <v>154</v>
       </c>
     </row>
@@ -3945,13 +3944,13 @@
       <c r="D92" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E92" s="3">
+      <c r="E92" s="2">
         <v>2.1</v>
       </c>
-      <c r="F92" s="3">
+      <c r="F92" s="2">
         <v>44</v>
       </c>
-      <c r="G92" s="6">
+      <c r="G92" s="5">
         <v>21</v>
       </c>
     </row>
@@ -3968,17 +3967,17 @@
       <c r="D93" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E93" s="3">
+      <c r="E93" s="2">
         <v>4.04</v>
       </c>
-      <c r="F93" s="3">
+      <c r="F93" s="2">
         <v>60.5</v>
       </c>
-      <c r="G93" s="6">
+      <c r="G93" s="5">
         <v>15</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>156</v>
       </c>
@@ -3991,17 +3990,17 @@
       <c r="D94" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E94" s="3">
+      <c r="E94" s="2">
         <v>12.99</v>
       </c>
-      <c r="F94" s="3">
+      <c r="F94" s="2">
         <v>12.99</v>
       </c>
-      <c r="G94" s="6">
+      <c r="G94" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>158</v>
       </c>
@@ -4014,17 +4013,17 @@
       <c r="D95" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E95" s="3">
+      <c r="E95" s="2">
         <v>1.49</v>
       </c>
-      <c r="F95" s="3">
+      <c r="F95" s="2">
         <v>29.8</v>
       </c>
-      <c r="G95" s="6">
+      <c r="G95" s="5">
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>160</v>
       </c>
@@ -4037,17 +4036,17 @@
       <c r="D96" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E96" s="3">
+      <c r="E96" s="2">
         <v>0.4</v>
       </c>
-      <c r="F96" s="3">
+      <c r="F96" s="2">
         <v>25.6</v>
       </c>
-      <c r="G96" s="6">
+      <c r="G96" s="5">
         <v>63</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>162</v>
       </c>
@@ -4060,17 +4059,17 @@
       <c r="D97" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E97" s="3">
+      <c r="E97" s="2">
         <v>0.52</v>
       </c>
-      <c r="F97" s="3">
+      <c r="F97" s="2">
         <v>8.9</v>
       </c>
-      <c r="G97" s="6">
+      <c r="G97" s="5">
         <v>17</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>164</v>
       </c>
@@ -4083,13 +4082,13 @@
       <c r="D98" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E98" s="3">
+      <c r="E98" s="2">
         <v>5.4</v>
       </c>
-      <c r="F98" s="3">
+      <c r="F98" s="2">
         <v>5.4</v>
       </c>
-      <c r="G98" s="6">
+      <c r="G98" s="5">
         <v>1</v>
       </c>
     </row>
@@ -4106,13 +4105,13 @@
       <c r="D99" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E99" s="3">
+      <c r="E99" s="2">
         <v>1.5</v>
       </c>
-      <c r="F99" s="3">
+      <c r="F99" s="2">
         <v>18</v>
       </c>
-      <c r="G99" s="6">
+      <c r="G99" s="5">
         <v>12</v>
       </c>
     </row>
@@ -4129,13 +4128,13 @@
       <c r="D100" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E100" s="3">
+      <c r="E100" s="2">
         <v>1.5</v>
       </c>
-      <c r="F100" s="3">
+      <c r="F100" s="2">
         <v>18</v>
       </c>
-      <c r="G100" s="6">
+      <c r="G100" s="5">
         <v>12</v>
       </c>
     </row>
@@ -4152,13 +4151,13 @@
       <c r="D101" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E101" s="3">
+      <c r="E101" s="2">
         <v>1.5</v>
       </c>
-      <c r="F101" s="3">
+      <c r="F101" s="2">
         <v>18</v>
       </c>
-      <c r="G101" s="6">
+      <c r="G101" s="5">
         <v>12</v>
       </c>
     </row>
@@ -4175,13 +4174,13 @@
       <c r="D102" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E102" s="3">
+      <c r="E102" s="2">
         <v>1.5</v>
       </c>
-      <c r="F102" s="3">
+      <c r="F102" s="2">
         <v>18</v>
       </c>
-      <c r="G102" s="6">
+      <c r="G102" s="5">
         <v>12</v>
       </c>
     </row>
@@ -4198,13 +4197,13 @@
       <c r="D103" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E103" s="3">
+      <c r="E103" s="2">
         <v>21</v>
       </c>
-      <c r="F103" s="3">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="G103" s="6">
+      <c r="F103" s="2">
+        <v>21</v>
+      </c>
+      <c r="G103" s="5">
         <v>1</v>
       </c>
     </row>
@@ -4215,19 +4214,19 @@
       <c r="B104" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="C104" t="s">
         <v>248</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E104" s="3">
+      <c r="E104" s="2">
         <v>24.9</v>
       </c>
-      <c r="F104" s="3">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="G104" s="6">
+      <c r="F104" s="2">
+        <v>24.9</v>
+      </c>
+      <c r="G104" s="5">
         <v>1</v>
       </c>
     </row>
@@ -4238,19 +4237,19 @@
       <c r="B105" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C105" s="2" t="s">
+      <c r="C105" t="s">
         <v>249</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E105" s="3">
+      <c r="E105" s="2">
         <v>21</v>
       </c>
-      <c r="F105" s="3">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="G105" s="6">
+      <c r="F105" s="2">
+        <v>21</v>
+      </c>
+      <c r="G105" s="5">
         <v>1</v>
       </c>
     </row>
@@ -4261,19 +4260,19 @@
       <c r="B106" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="C106" t="s">
         <v>250</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E106" s="3">
+      <c r="E106" s="2">
         <v>21</v>
       </c>
-      <c r="F106" s="3">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="G106" s="6">
+      <c r="F106" s="2">
+        <v>21</v>
+      </c>
+      <c r="G106" s="5">
         <v>1</v>
       </c>
     </row>
@@ -4284,19 +4283,19 @@
       <c r="B107" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C107" s="2" t="s">
+      <c r="C107" t="s">
         <v>251</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E107" s="3">
+      <c r="E107" s="2">
         <v>21</v>
       </c>
-      <c r="F107" s="3">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="G107" s="6">
+      <c r="F107" s="2">
+        <v>21</v>
+      </c>
+      <c r="G107" s="5">
         <v>1</v>
       </c>
     </row>
@@ -4307,19 +4306,19 @@
       <c r="B108" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C108" s="2" t="s">
+      <c r="C108" t="s">
         <v>252</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E108" s="3">
+      <c r="E108" s="2">
         <v>21</v>
       </c>
-      <c r="F108" s="3">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="G108" s="6">
+      <c r="F108" s="2">
+        <v>21</v>
+      </c>
+      <c r="G108" s="5">
         <v>1</v>
       </c>
     </row>
@@ -4330,19 +4329,19 @@
       <c r="B109" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C109" s="2" t="s">
+      <c r="C109" t="s">
         <v>253</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E109" s="3">
+      <c r="E109" s="2">
         <v>21</v>
       </c>
-      <c r="F109" s="3">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="G109" s="6">
+      <c r="F109" s="2">
+        <v>21</v>
+      </c>
+      <c r="G109" s="5">
         <v>1</v>
       </c>
     </row>
@@ -4353,19 +4352,19 @@
       <c r="B110" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C110" s="2" t="s">
+      <c r="C110" t="s">
         <v>254</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E110" s="3">
+      <c r="E110" s="2">
         <v>21</v>
       </c>
-      <c r="F110" s="3">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="G110" s="6">
+      <c r="F110" s="2">
+        <v>21</v>
+      </c>
+      <c r="G110" s="5">
         <v>1</v>
       </c>
     </row>
@@ -4376,19 +4375,19 @@
       <c r="B111" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C111" s="2" t="s">
+      <c r="C111" t="s">
         <v>255</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E111" s="3">
+      <c r="E111" s="2">
         <v>21</v>
       </c>
-      <c r="F111" s="3">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="G111" s="6">
+      <c r="F111" s="2">
+        <v>21</v>
+      </c>
+      <c r="G111" s="5">
         <v>1</v>
       </c>
     </row>
@@ -4399,203 +4398,203 @@
       <c r="B112" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C112" s="2" t="s">
+      <c r="C112" t="s">
         <v>256</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E112" s="3">
+      <c r="E112" s="2">
         <v>21</v>
       </c>
-      <c r="F112" s="3">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="G112" s="6">
+      <c r="F112" s="2">
+        <v>21</v>
+      </c>
+      <c r="G112" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>221</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C113" s="2" t="s">
+      <c r="C113" t="s">
         <v>225</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="E113" s="3">
+      <c r="E113" s="2">
         <v>6.81</v>
       </c>
-      <c r="F113" s="3">
-        <v>81.72</v>
-      </c>
-      <c r="G113" s="7">
+      <c r="F113" s="2">
+        <v>6.81</v>
+      </c>
+      <c r="G113" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>224</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="C114" t="s">
         <v>226</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="E114" s="3">
+      <c r="E114" s="2">
         <v>4.04</v>
       </c>
-      <c r="F114" s="3">
-        <v>48.48</v>
-      </c>
-      <c r="G114" s="7">
+      <c r="F114" s="2">
+        <v>4.04</v>
+      </c>
+      <c r="G114" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>228</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C115" s="2" t="s">
+      <c r="C115" t="s">
         <v>229</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="E115" s="3">
+      <c r="E115" s="2">
         <v>9.06</v>
       </c>
-      <c r="F115" s="3">
-        <v>54.36</v>
-      </c>
-      <c r="G115" s="7">
+      <c r="F115" s="2">
+        <v>9.06</v>
+      </c>
+      <c r="G115" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>230</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C116" s="2" t="s">
+      <c r="C116" t="s">
         <v>231</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="E116" s="3">
+      <c r="E116" s="2">
         <v>9.2100000000000009</v>
       </c>
-      <c r="F116" s="3">
-        <v>55.26</v>
-      </c>
-      <c r="G116" s="7">
+      <c r="F116" s="2">
+        <v>9.2100000000000009</v>
+      </c>
+      <c r="G116" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>232</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C117" s="2" t="s">
+      <c r="C117" t="s">
         <v>234</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="E117" s="3">
+      <c r="E117" s="2">
         <v>8.65</v>
       </c>
-      <c r="F117" s="3">
-        <v>103.8</v>
-      </c>
-      <c r="G117" s="7">
+      <c r="F117" s="2">
+        <v>8.65</v>
+      </c>
+      <c r="G117" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>233</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C118" s="2" t="s">
+      <c r="C118" t="s">
         <v>235</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="E118" s="3">
+      <c r="E118" s="2">
         <v>8.8800000000000008</v>
       </c>
-      <c r="F118" s="3">
-        <v>106.56</v>
-      </c>
-      <c r="G118" s="7">
+      <c r="F118" s="2">
+        <v>8.8800000000000008</v>
+      </c>
+      <c r="G118" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>236</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C119" s="2" t="s">
+      <c r="C119" t="s">
         <v>237</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="E119" s="3">
+      <c r="E119" s="2">
         <v>6.42</v>
       </c>
-      <c r="F119" s="3">
-        <v>77.040000000000006</v>
-      </c>
-      <c r="G119" s="7">
+      <c r="F119" s="2">
+        <v>6.42</v>
+      </c>
+      <c r="G119" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>238</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C120" s="2" t="s">
+      <c r="C120" t="s">
         <v>239</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="E120" s="3">
+      <c r="E120" s="2">
         <v>6.26</v>
       </c>
-      <c r="F120" s="3">
-        <v>75.12</v>
-      </c>
-      <c r="G120" s="7">
+      <c r="F120" s="2">
+        <v>6.26</v>
+      </c>
+      <c r="G120" s="6">
         <v>1</v>
       </c>
     </row>
@@ -4606,19 +4605,19 @@
       <c r="B121" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C121" s="2" t="s">
+      <c r="C121" t="s">
         <v>246</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E121" s="3">
+      <c r="E121" s="2">
         <v>0.93</v>
       </c>
-      <c r="F121" s="3">
+      <c r="F121" s="2">
         <v>21.43</v>
       </c>
-      <c r="G121" s="6">
+      <c r="G121" s="5">
         <v>23</v>
       </c>
     </row>
@@ -4629,19 +4628,19 @@
       <c r="B122" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C122" s="2" t="s">
+      <c r="C122" t="s">
         <v>245</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E122" s="3">
+      <c r="E122" s="2">
         <v>0.43</v>
       </c>
-      <c r="F122" s="3">
+      <c r="F122" s="2">
         <v>21.43</v>
       </c>
-      <c r="G122" s="6">
+      <c r="G122" s="5">
         <v>50</v>
       </c>
     </row>
@@ -4652,19 +4651,19 @@
       <c r="B123" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C123" s="2" t="s">
+      <c r="C123" t="s">
         <v>243</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E123" s="3">
+      <c r="E123" s="2">
         <v>2.36</v>
       </c>
-      <c r="F123" s="3">
+      <c r="F123" s="2">
         <v>47.14</v>
       </c>
-      <c r="G123" s="6">
+      <c r="G123" s="5">
         <v>20</v>
       </c>
     </row>
@@ -4675,19 +4674,19 @@
       <c r="B124" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C124" s="2" t="s">
+      <c r="C124" t="s">
         <v>257</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E124" s="3">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="F124" s="3">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="G124" s="6">
+      <c r="E124" s="2">
+        <v>21</v>
+      </c>
+      <c r="F124" s="2">
+        <v>21</v>
+      </c>
+      <c r="G124" s="5">
         <v>1</v>
       </c>
     </row>
@@ -4698,19 +4697,19 @@
       <c r="B125" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C125" s="2" t="s">
+      <c r="C125" t="s">
         <v>258</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E125" s="3">
+      <c r="E125" s="2">
         <v>16</v>
       </c>
-      <c r="F125" s="3">
+      <c r="F125" s="2">
         <v>16</v>
       </c>
-      <c r="G125" s="6" t="s">
+      <c r="G125" s="5" t="s">
         <v>259</v>
       </c>
     </row>
@@ -4721,19 +4720,19 @@
       <c r="B126" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C126" s="2" t="s">
+      <c r="C126" t="s">
         <v>283</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E126" s="3">
+      <c r="E126" s="2">
         <v>2.1</v>
       </c>
-      <c r="F126" s="3">
+      <c r="F126" s="2">
         <v>50.4</v>
       </c>
-      <c r="G126" s="6">
+      <c r="G126" s="5">
         <v>24</v>
       </c>
     </row>
@@ -4744,203 +4743,203 @@
       <c r="B127" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C127" s="2" t="s">
+      <c r="C127" t="s">
         <v>263</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E127" s="3">
+      <c r="E127" s="2">
         <v>5.3</v>
       </c>
-      <c r="F127" s="3">
+      <c r="F127" s="2">
         <v>127</v>
       </c>
-      <c r="G127" s="6">
+      <c r="G127" s="5">
         <v>24</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>264</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C128" s="2" t="s">
+      <c r="C128" t="s">
         <v>265</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="E128" s="3">
+      <c r="E128" s="2">
         <v>5.69</v>
       </c>
-      <c r="F128" s="3">
+      <c r="F128" s="2">
         <v>68.28</v>
       </c>
-      <c r="G128" s="6">
+      <c r="G128" s="5">
         <v>12</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>272</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C129" s="2" t="s">
+      <c r="C129" t="s">
         <v>267</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="E129" s="3">
+      <c r="E129" s="2">
         <v>5.69</v>
       </c>
-      <c r="F129" s="3">
+      <c r="F129" s="2">
         <v>68.28</v>
       </c>
-      <c r="G129" s="6">
+      <c r="G129" s="5">
         <v>12</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>273</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C130" s="2" t="s">
+      <c r="C130" t="s">
         <v>268</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="E130" s="3">
+      <c r="E130" s="2">
         <v>5.69</v>
       </c>
-      <c r="F130" s="3">
+      <c r="F130" s="2">
         <v>68.28</v>
       </c>
-      <c r="G130" s="6">
+      <c r="G130" s="5">
         <v>12</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>274</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C131" s="2" t="s">
+      <c r="C131" t="s">
         <v>269</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="E131" s="3">
+      <c r="E131" s="2">
         <v>5.69</v>
       </c>
-      <c r="F131" s="3">
+      <c r="F131" s="2">
         <v>68.28</v>
       </c>
-      <c r="G131" s="6">
+      <c r="G131" s="5">
         <v>12</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>275</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C132" s="2" t="s">
+      <c r="C132" t="s">
         <v>270</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="E132" s="3">
+      <c r="E132" s="2">
         <v>5.69</v>
       </c>
-      <c r="F132" s="3">
+      <c r="F132" s="2">
         <v>68.28</v>
       </c>
-      <c r="G132" s="6">
+      <c r="G132" s="5">
         <v>12</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>276</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C133" s="2" t="s">
+      <c r="C133" t="s">
         <v>271</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="E133" s="3">
+      <c r="E133" s="2">
         <v>6.99</v>
       </c>
-      <c r="F133" s="3">
+      <c r="F133" s="2">
         <v>69.900000000000006</v>
       </c>
-      <c r="G133" s="6">
+      <c r="G133" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>279</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C134" s="2" t="s">
+      <c r="C134" t="s">
         <v>277</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="E134" s="3">
+      <c r="E134" s="2">
         <v>6.99</v>
       </c>
-      <c r="F134" s="3">
+      <c r="F134" s="2">
         <v>69.900000000000006</v>
       </c>
-      <c r="G134" s="6">
+      <c r="G134" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>280</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C135" s="2" t="s">
+      <c r="C135" t="s">
         <v>278</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="E135" s="3">
+      <c r="E135" s="2">
         <v>6.99</v>
       </c>
-      <c r="F135" s="3">
+      <c r="F135" s="2">
         <v>69.900000000000006</v>
       </c>
-      <c r="G135" s="6">
+      <c r="G135" s="5">
         <v>10</v>
       </c>
     </row>
@@ -4951,46 +4950,53 @@
       <c r="B136" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C136" s="2" t="s">
+      <c r="C136" t="s">
         <v>282</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E136" s="3">
+      <c r="E136" s="2">
         <v>2.2599999999999998</v>
       </c>
-      <c r="F136" s="3">
+      <c r="F136" s="2">
         <v>54.29</v>
       </c>
-      <c r="G136" s="6">
+      <c r="G136" s="5">
         <v>24</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>294</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C137" s="2" t="s">
+      <c r="C137" t="s">
         <v>227</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="E137" s="3">
+      <c r="E137" s="2">
         <v>4.08</v>
       </c>
-      <c r="F137" s="3">
-        <v>48.96</v>
-      </c>
-      <c r="G137" s="6">
+      <c r="F137" s="2">
+        <v>4.08</v>
+      </c>
+      <c r="G137" s="5">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G137" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="WK"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1cfefa7afb5b64df/bsbox/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="255" documentId="13_ncr:1_{54C4E61B-1CE2-4548-BDA4-A6B0798C7B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EFAD67A-35B5-48D6-B441-AC2F04256476}"/>
+  <xr:revisionPtr revIDLastSave="273" documentId="13_ncr:1_{54C4E61B-1CE2-4548-BDA4-A6B0798C7B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FD7C865-A713-44B4-BE8E-6685FD18CA7B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="base_de_produtos" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">base_de_produtos!$A$1:$G$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">base_de_produtos!$A$1:$G$138</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="297">
   <si>
     <t>categoria</t>
   </si>
@@ -908,6 +908,12 @@
   </si>
   <si>
     <t>04060009</t>
+  </si>
+  <si>
+    <t>01030610</t>
+  </si>
+  <si>
+    <t>Doce de Leite com Coco No Ponto pote com 20 Unid</t>
   </si>
 </sst>
 </file>
@@ -1782,8 +1788,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:J137"/>
+  <dimension ref="A1:J138"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -1818,7 +1823,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>115</v>
       </c>
@@ -1841,7 +1846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>116</v>
       </c>
@@ -1864,7 +1869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>117</v>
       </c>
@@ -1887,7 +1892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>118</v>
       </c>
@@ -1910,7 +1915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>119</v>
       </c>
@@ -1933,7 +1938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>120</v>
       </c>
@@ -1956,7 +1961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>121</v>
       </c>
@@ -1979,7 +1984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>122</v>
       </c>
@@ -2002,7 +2007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>123</v>
       </c>
@@ -2025,7 +2030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>105</v>
       </c>
@@ -2048,7 +2053,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>106</v>
       </c>
@@ -2071,7 +2076,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>107</v>
       </c>
@@ -2094,7 +2099,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>108</v>
       </c>
@@ -2117,7 +2122,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>109</v>
       </c>
@@ -2140,7 +2145,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>110</v>
       </c>
@@ -2163,7 +2168,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>111</v>
       </c>
@@ -2186,7 +2191,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>112</v>
       </c>
@@ -2209,7 +2214,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>113</v>
       </c>
@@ -2232,7 +2237,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>114</v>
       </c>
@@ -2255,7 +2260,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>134</v>
       </c>
@@ -2279,7 +2284,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>137</v>
       </c>
@@ -2303,7 +2308,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>138</v>
       </c>
@@ -2327,7 +2332,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>141</v>
       </c>
@@ -2351,7 +2356,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>142</v>
       </c>
@@ -2375,7 +2380,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>144</v>
       </c>
@@ -2399,7 +2404,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>29</v>
       </c>
@@ -2422,7 +2427,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>30</v>
       </c>
@@ -2445,7 +2450,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>31</v>
       </c>
@@ -2468,7 +2473,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>32</v>
       </c>
@@ -2491,7 +2496,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>33</v>
       </c>
@@ -2514,7 +2519,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>34</v>
       </c>
@@ -2537,7 +2542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>35</v>
       </c>
@@ -2560,7 +2565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>36</v>
       </c>
@@ -2583,7 +2588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>37</v>
       </c>
@@ -2606,7 +2611,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>38</v>
       </c>
@@ -2629,7 +2634,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>39</v>
       </c>
@@ -2652,7 +2657,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>40</v>
       </c>
@@ -2675,7 +2680,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>41</v>
       </c>
@@ -2698,7 +2703,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>42</v>
       </c>
@@ -2721,7 +2726,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>43</v>
       </c>
@@ -2744,7 +2749,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>44</v>
       </c>
@@ -2767,7 +2772,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>45</v>
       </c>
@@ -2790,7 +2795,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>46</v>
       </c>
@@ -2813,7 +2818,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>47</v>
       </c>
@@ -2836,7 +2841,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>48</v>
       </c>
@@ -2859,7 +2864,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>49</v>
       </c>
@@ -2905,7 +2910,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>69</v>
       </c>
@@ -2928,7 +2933,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>70</v>
       </c>
@@ -2951,7 +2956,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>71</v>
       </c>
@@ -2974,7 +2979,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>72</v>
       </c>
@@ -2997,7 +3002,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>73</v>
       </c>
@@ -3020,7 +3025,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>74</v>
       </c>
@@ -3043,7 +3048,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>75</v>
       </c>
@@ -3066,7 +3071,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>76</v>
       </c>
@@ -3089,7 +3094,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>94</v>
       </c>
@@ -3112,7 +3117,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>78</v>
       </c>
@@ -3126,20 +3131,20 @@
         <v>67</v>
       </c>
       <c r="E58" s="4">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="F58" s="2">
-        <v>42.9</v>
+        <v>45</v>
       </c>
       <c r="G58" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="H58">
-        <f>48.4/50</f>
-        <v>0.96799999999999997</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I58">
+        <f>45/20</f>
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>79</v>
       </c>
@@ -3162,7 +3167,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>80</v>
       </c>
@@ -3185,7 +3190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>81</v>
       </c>
@@ -3208,7 +3213,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>82</v>
       </c>
@@ -3231,7 +3236,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>83</v>
       </c>
@@ -3254,7 +3259,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>84</v>
       </c>
@@ -3740,7 +3745,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>129</v>
       </c>
@@ -3945,10 +3950,10 @@
         <v>67</v>
       </c>
       <c r="E92" s="2">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="F92" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G92" s="5">
         <v>21</v>
@@ -3977,7 +3982,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>156</v>
       </c>
@@ -4000,7 +4005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>158</v>
       </c>
@@ -4023,7 +4028,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>160</v>
       </c>
@@ -4046,7 +4051,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>162</v>
       </c>
@@ -4069,7 +4074,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>164</v>
       </c>
@@ -4414,7 +4419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>221</v>
       </c>
@@ -4437,7 +4442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>224</v>
       </c>
@@ -4460,7 +4465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>228</v>
       </c>
@@ -4483,7 +4488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>230</v>
       </c>
@@ -4506,7 +4511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>232</v>
       </c>
@@ -4529,7 +4534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>233</v>
       </c>
@@ -4552,7 +4557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>236</v>
       </c>
@@ -4575,7 +4580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>238</v>
       </c>
@@ -4727,10 +4732,10 @@
         <v>67</v>
       </c>
       <c r="E126" s="2">
-        <v>2.1</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="F126" s="2">
-        <v>50.4</v>
+        <v>54.29</v>
       </c>
       <c r="G126" s="5">
         <v>24</v>
@@ -4759,7 +4764,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>264</v>
       </c>
@@ -4782,7 +4787,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>272</v>
       </c>
@@ -4805,7 +4810,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>273</v>
       </c>
@@ -4828,7 +4833,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>274</v>
       </c>
@@ -4851,7 +4856,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>275</v>
       </c>
@@ -4874,7 +4879,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>276</v>
       </c>
@@ -4897,7 +4902,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>279</v>
       </c>
@@ -4920,7 +4925,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>280</v>
       </c>
@@ -4966,7 +4971,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>294</v>
       </c>
@@ -4989,14 +4994,31 @@
         <v>1</v>
       </c>
     </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C138" t="s">
+        <v>296</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E138" s="2">
+        <v>2.25</v>
+      </c>
+      <c r="F138" s="2">
+        <v>45</v>
+      </c>
+      <c r="G138" s="3">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G137" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="WK"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:G138" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1CFEFA7AFB5B64DF/bsbox/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{32DF9513-3448-4E5B-8499-1BE121EF9C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D7346E0-9F2E-4C68-8EFA-057C4EDB9D0D}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{32DF9513-3448-4E5B-8499-1BE121EF9C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81087BF8-A02A-4CDE-86E3-F59700A74DB8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="260">
   <si>
     <t>categoria</t>
   </si>
@@ -794,6 +794,15 @@
   </si>
   <si>
     <t>DWK Beijo Chocolate Ouro de Minas Pote com 21 Unid</t>
+  </si>
+  <si>
+    <t>L1030552</t>
+  </si>
+  <si>
+    <t>L1030613</t>
+  </si>
+  <si>
+    <t>01030613</t>
   </si>
 </sst>
 </file>
@@ -1298,18 +1307,18 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="47" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="47" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="47" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="48">
@@ -1672,16 +1681,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}">
-  <dimension ref="A1:J124"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="74.5703125" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" style="4" customWidth="1"/>
     <col min="6" max="6" width="15.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1703,7 +1712,7 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1726,7 +1735,7 @@
       <c r="F2" s="2">
         <v>59.9</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="7">
         <v>10</v>
       </c>
     </row>
@@ -1749,7 +1758,7 @@
       <c r="F3" s="2">
         <v>59.9</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="7">
         <v>10</v>
       </c>
     </row>
@@ -1772,7 +1781,7 @@
       <c r="F4" s="2">
         <v>59.9</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="7">
         <v>10</v>
       </c>
     </row>
@@ -1795,7 +1804,7 @@
       <c r="F5" s="2">
         <v>59.9</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="7">
         <v>10</v>
       </c>
     </row>
@@ -1818,7 +1827,7 @@
       <c r="F6" s="2">
         <v>59.9</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="7">
         <v>10</v>
       </c>
     </row>
@@ -1841,7 +1850,7 @@
       <c r="F7" s="2">
         <v>59.9</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="7">
         <v>10</v>
       </c>
     </row>
@@ -1864,7 +1873,7 @@
       <c r="F8" s="2">
         <v>59.9</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="7">
         <v>10</v>
       </c>
     </row>
@@ -1887,7 +1896,7 @@
       <c r="F9" s="2">
         <v>59.9</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="7">
         <v>10</v>
       </c>
     </row>
@@ -1910,7 +1919,7 @@
       <c r="F10" s="2">
         <v>84</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="7">
         <v>24</v>
       </c>
     </row>
@@ -1933,7 +1942,7 @@
       <c r="F11" s="2">
         <v>84</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="7">
         <v>24</v>
       </c>
     </row>
@@ -1957,7 +1966,7 @@
         <f>E12*24</f>
         <v>47.76</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="7">
         <v>24</v>
       </c>
     </row>
@@ -1981,7 +1990,7 @@
         <f t="shared" ref="F13:F17" si="0">E13*24</f>
         <v>47.76</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="7">
         <v>24</v>
       </c>
     </row>
@@ -2005,7 +2014,7 @@
         <f t="shared" si="0"/>
         <v>47.76</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="7">
         <v>24</v>
       </c>
     </row>
@@ -2029,7 +2038,7 @@
         <f t="shared" si="0"/>
         <v>47.76</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="7">
         <v>24</v>
       </c>
     </row>
@@ -2053,11 +2062,11 @@
         <f t="shared" si="0"/>
         <v>47.76</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="7">
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>78</v>
       </c>
@@ -2077,11 +2086,11 @@
         <f t="shared" si="0"/>
         <v>47.76</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="7">
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
@@ -2094,18 +2103,17 @@
       <c r="D18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="5">
         <v>2.0533333333333337</v>
       </c>
       <c r="F18" s="2">
         <v>61.600000000000009</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="7">
         <v>30</v>
       </c>
-      <c r="H18" s="1"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
@@ -2118,18 +2126,17 @@
       <c r="D19" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="5">
         <v>5.23</v>
       </c>
       <c r="F19" s="2">
         <v>104.50000000000001</v>
       </c>
-      <c r="G19" s="5">
-        <v>20</v>
-      </c>
-      <c r="H19" s="1"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G19" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
@@ -2142,18 +2149,17 @@
       <c r="D20" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="5">
         <v>2.2000000000000002</v>
       </c>
       <c r="F20" s="2">
         <v>48.400000000000006</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G20" s="7">
         <v>22</v>
       </c>
-      <c r="H20" s="1"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>24</v>
       </c>
@@ -2166,18 +2172,17 @@
       <c r="D21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="5">
         <v>2.2000000000000002</v>
       </c>
       <c r="F21" s="2">
         <v>48.400000000000006</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G21" s="7">
         <v>22</v>
       </c>
-      <c r="H21" s="1"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
@@ -2190,18 +2195,17 @@
       <c r="D22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E22" s="5">
         <v>2.86</v>
       </c>
       <c r="F22" s="2">
         <v>57.2</v>
       </c>
-      <c r="G22" s="5">
-        <v>20</v>
-      </c>
-      <c r="H22" s="1"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G22" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>26</v>
       </c>
@@ -2214,18 +2218,17 @@
       <c r="D23" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="5">
         <v>3.08</v>
       </c>
       <c r="F23" s="2">
         <v>61.600000000000009</v>
       </c>
-      <c r="G23" s="5">
-        <v>20</v>
-      </c>
-      <c r="H23" s="1"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G23" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>27</v>
       </c>
@@ -2238,18 +2241,17 @@
       <c r="D24" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="5">
         <v>2.75</v>
       </c>
       <c r="F24" s="2">
         <v>66</v>
       </c>
-      <c r="G24" s="5">
+      <c r="G24" s="7">
         <v>24</v>
       </c>
-      <c r="H24" s="1"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>28</v>
       </c>
@@ -2262,18 +2264,17 @@
       <c r="D25" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="5">
         <v>4.4000000000000004</v>
       </c>
       <c r="F25" s="2">
         <v>88</v>
       </c>
-      <c r="G25" s="5">
-        <v>20</v>
-      </c>
-      <c r="H25" s="1"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G25" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>29</v>
       </c>
@@ -2286,18 +2287,17 @@
       <c r="D26" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="5">
         <v>2.57</v>
       </c>
       <c r="F26" s="2">
         <v>61.600000000000009</v>
       </c>
-      <c r="G26" s="5">
+      <c r="G26" s="7">
         <v>24</v>
       </c>
-      <c r="H26" s="1"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>47</v>
       </c>
@@ -2310,18 +2310,17 @@
       <c r="D27" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E27" s="5">
         <v>2.57</v>
       </c>
       <c r="F27" s="2">
         <v>61.600000000000009</v>
       </c>
-      <c r="G27" s="5">
+      <c r="G27" s="7">
         <v>24</v>
       </c>
-      <c r="H27" s="1"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>31</v>
       </c>
@@ -2334,18 +2333,17 @@
       <c r="D28" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E28" s="5">
         <v>2.25</v>
       </c>
       <c r="F28" s="2">
         <v>45</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="G28" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="H28" s="1"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>32</v>
       </c>
@@ -2358,18 +2356,17 @@
       <c r="D29" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E29" s="7">
+      <c r="E29" s="5">
         <v>2.75</v>
       </c>
       <c r="F29" s="2">
         <v>82.5</v>
       </c>
-      <c r="G29" s="5">
+      <c r="G29" s="7">
         <v>30</v>
       </c>
-      <c r="H29" s="1"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>33</v>
       </c>
@@ -2382,18 +2379,17 @@
       <c r="D30" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E30" s="5">
         <v>14.3</v>
       </c>
       <c r="F30" s="2">
         <v>14.3</v>
       </c>
-      <c r="G30" s="5">
+      <c r="G30" s="7">
         <v>1</v>
       </c>
-      <c r="H30" s="1"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>34</v>
       </c>
@@ -2406,18 +2402,17 @@
       <c r="D31" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E31" s="5">
         <v>15</v>
       </c>
       <c r="F31" s="2">
         <v>225.50000000000003</v>
       </c>
-      <c r="G31" s="5">
+      <c r="G31" s="7">
         <v>15</v>
       </c>
-      <c r="H31" s="1"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>35</v>
       </c>
@@ -2430,18 +2425,17 @@
       <c r="D32" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E32" s="7">
+      <c r="E32" s="5">
         <v>1.54</v>
       </c>
       <c r="F32" s="2">
         <v>46.2</v>
       </c>
-      <c r="G32" s="5">
+      <c r="G32" s="7">
         <v>30</v>
       </c>
-      <c r="H32" s="1"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>36</v>
       </c>
@@ -2454,18 +2448,17 @@
       <c r="D33" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E33" s="5">
         <v>2.2000000000000002</v>
       </c>
       <c r="F33" s="2">
         <v>48.400000000000006</v>
       </c>
-      <c r="G33" s="5">
+      <c r="G33" s="7">
         <v>22</v>
       </c>
-      <c r="H33" s="1"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>37</v>
       </c>
@@ -2478,18 +2471,17 @@
       <c r="D34" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E34" s="5">
         <v>2.2000000000000002</v>
       </c>
       <c r="F34" s="2">
         <v>48.400000000000006</v>
       </c>
-      <c r="G34" s="5">
+      <c r="G34" s="7">
         <v>22</v>
       </c>
-      <c r="H34" s="1"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>38</v>
       </c>
@@ -2502,18 +2494,17 @@
       <c r="D35" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E35" s="5">
         <v>2.2000000000000002</v>
       </c>
       <c r="F35" s="2">
         <v>48.400000000000006</v>
       </c>
-      <c r="G35" s="5">
+      <c r="G35" s="7">
         <v>22</v>
       </c>
-      <c r="H35" s="1"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>39</v>
       </c>
@@ -2526,19 +2517,17 @@
       <c r="D36" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E36" s="7">
+      <c r="E36" s="5">
         <v>7.5</v>
       </c>
       <c r="F36" s="2">
         <v>150</v>
       </c>
-      <c r="G36" s="5">
-        <v>20</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G36" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>40</v>
       </c>
@@ -2551,18 +2540,17 @@
       <c r="D37" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E37" s="7">
+      <c r="E37" s="5">
         <v>4.03</v>
       </c>
       <c r="F37" s="2">
         <v>60.500000000000007</v>
       </c>
-      <c r="G37" s="5">
+      <c r="G37" s="7">
         <v>15</v>
       </c>
-      <c r="H37" s="1"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>41</v>
       </c>
@@ -2575,18 +2563,17 @@
       <c r="D38" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E38" s="7">
+      <c r="E38" s="5">
         <v>5.5</v>
       </c>
       <c r="F38" s="2">
         <v>82.5</v>
       </c>
-      <c r="G38" s="5">
+      <c r="G38" s="7">
         <v>15</v>
       </c>
-      <c r="H38" s="1"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>42</v>
       </c>
@@ -2599,18 +2586,17 @@
       <c r="D39" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E39" s="7">
+      <c r="E39" s="5">
         <v>3.38</v>
       </c>
       <c r="F39" s="2">
         <v>141.9</v>
       </c>
-      <c r="G39" s="5">
+      <c r="G39" s="7">
         <v>42</v>
       </c>
-      <c r="H39" s="1"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>43</v>
       </c>
@@ -2623,18 +2609,17 @@
       <c r="D40" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="7">
+      <c r="E40" s="5">
         <v>2.42</v>
       </c>
       <c r="F40" s="2">
         <v>48.400000000000006</v>
       </c>
-      <c r="G40" s="5">
-        <v>20</v>
-      </c>
-      <c r="H40" s="1"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G40" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>44</v>
       </c>
@@ -2647,18 +2632,17 @@
       <c r="D41" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E41" s="7">
+      <c r="E41" s="5">
         <v>2.17</v>
       </c>
       <c r="F41" s="2">
         <v>91.300000000000011</v>
       </c>
-      <c r="G41" s="5">
+      <c r="G41" s="7">
         <v>42</v>
       </c>
-      <c r="H41" s="1"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>45</v>
       </c>
@@ -2671,18 +2655,17 @@
       <c r="D42" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="7">
+      <c r="E42" s="5">
         <v>1.38</v>
       </c>
       <c r="F42" s="2">
         <v>48.400000000000006</v>
       </c>
-      <c r="G42" s="5">
+      <c r="G42" s="7">
         <v>35</v>
       </c>
-      <c r="H42" s="1"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>46</v>
       </c>
@@ -2695,18 +2678,17 @@
       <c r="D43" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="7">
+      <c r="E43" s="5">
         <v>5.65</v>
       </c>
       <c r="F43" s="2">
         <v>84.7</v>
       </c>
-      <c r="G43" s="5">
+      <c r="G43" s="7">
         <v>15</v>
       </c>
-      <c r="H43" s="1"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>48</v>
       </c>
@@ -2719,18 +2701,17 @@
       <c r="D44" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E44" s="7">
+      <c r="E44" s="5">
         <v>5.65</v>
       </c>
       <c r="F44" s="2">
         <v>84.7</v>
       </c>
-      <c r="G44" s="5">
+      <c r="G44" s="7">
         <v>15</v>
       </c>
-      <c r="H44" s="1"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>49</v>
       </c>
@@ -2743,18 +2724,17 @@
       <c r="D45" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E45" s="7">
+      <c r="E45" s="5">
         <v>5.65</v>
       </c>
       <c r="F45" s="2">
         <v>84.7</v>
       </c>
-      <c r="G45" s="5">
+      <c r="G45" s="7">
         <v>15</v>
       </c>
-      <c r="H45" s="1"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>50</v>
       </c>
@@ -2767,18 +2747,17 @@
       <c r="D46" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="7">
+      <c r="E46" s="5">
         <v>5.65</v>
       </c>
       <c r="F46" s="2">
         <v>84.7</v>
       </c>
-      <c r="G46" s="5">
+      <c r="G46" s="7">
         <v>15</v>
       </c>
-      <c r="H46" s="1"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>51</v>
       </c>
@@ -2791,18 +2770,17 @@
       <c r="D47" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E47" s="7">
+      <c r="E47" s="5">
         <v>5.65</v>
       </c>
       <c r="F47" s="2">
         <v>84.7</v>
       </c>
-      <c r="G47" s="5">
+      <c r="G47" s="7">
         <v>15</v>
       </c>
-      <c r="H47" s="1"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>52</v>
       </c>
@@ -2815,18 +2793,17 @@
       <c r="D48" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E48" s="7">
+      <c r="E48" s="5">
         <v>5.65</v>
       </c>
       <c r="F48" s="2">
         <v>84.7</v>
       </c>
-      <c r="G48" s="5">
+      <c r="G48" s="7">
         <v>15</v>
       </c>
-      <c r="H48" s="1"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>53</v>
       </c>
@@ -2839,19 +2816,17 @@
       <c r="D49" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E49" s="7">
+      <c r="E49" s="5">
         <v>5.65</v>
       </c>
       <c r="F49" s="2">
         <v>84.7</v>
       </c>
-      <c r="G49" s="5">
+      <c r="G49" s="7">
         <v>15</v>
       </c>
-      <c r="H49" s="1"/>
-      <c r="J49" s="1"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>54</v>
       </c>
@@ -2864,18 +2839,17 @@
       <c r="D50" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E50" s="7">
+      <c r="E50" s="5">
         <v>4.6399999999999997</v>
       </c>
       <c r="F50" s="2">
         <v>111.43</v>
       </c>
-      <c r="G50" s="5">
+      <c r="G50" s="7">
         <v>24</v>
       </c>
-      <c r="H50" s="1"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>55</v>
       </c>
@@ -2888,18 +2862,17 @@
       <c r="D51" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E51" s="7">
+      <c r="E51" s="5">
         <v>2.14</v>
       </c>
       <c r="F51" s="2">
         <v>64.290000000000006</v>
       </c>
-      <c r="G51" s="5">
+      <c r="G51" s="7">
         <v>30</v>
       </c>
-      <c r="H51" s="1"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>56</v>
       </c>
@@ -2912,18 +2885,17 @@
       <c r="D52" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E52" s="7">
+      <c r="E52" s="5">
         <v>10.45</v>
       </c>
       <c r="F52" s="2">
         <v>10.450000000000001</v>
       </c>
-      <c r="G52" s="5">
+      <c r="G52" s="7">
         <v>1</v>
       </c>
-      <c r="H52" s="1"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>57</v>
       </c>
@@ -2936,18 +2908,17 @@
       <c r="D53" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E53" s="7">
+      <c r="E53" s="5">
         <v>2.52</v>
       </c>
       <c r="F53" s="2">
         <v>75.709999999999994</v>
       </c>
-      <c r="G53" s="5">
+      <c r="G53" s="7">
         <v>30</v>
       </c>
-      <c r="H53" s="1"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>80</v>
       </c>
@@ -2960,17 +2931,17 @@
       <c r="D54" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E54" s="7">
+      <c r="E54" s="5">
         <v>2.63</v>
       </c>
       <c r="F54" s="2">
         <v>52.64</v>
       </c>
-      <c r="G54" s="5">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G54" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>81</v>
       </c>
@@ -2983,17 +2954,17 @@
       <c r="D55" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E55" s="7">
+      <c r="E55" s="5">
         <v>2.63</v>
       </c>
       <c r="F55" s="2">
         <v>52.64</v>
       </c>
-      <c r="G55" s="5">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G55" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>82</v>
       </c>
@@ -3006,17 +2977,17 @@
       <c r="D56" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E56" s="7">
+      <c r="E56" s="5">
         <v>2.63</v>
       </c>
       <c r="F56" s="2">
         <v>52.64</v>
       </c>
-      <c r="G56" s="5">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G56" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>83</v>
       </c>
@@ -3029,17 +3000,17 @@
       <c r="D57" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E57" s="7">
+      <c r="E57" s="5">
         <v>2.14</v>
       </c>
       <c r="F57" s="2">
         <v>45</v>
       </c>
-      <c r="G57" s="5" t="s">
+      <c r="G57" s="7" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>84</v>
       </c>
@@ -3052,17 +3023,17 @@
       <c r="D58" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E58" s="7">
+      <c r="E58" s="5">
         <v>2.14</v>
       </c>
       <c r="F58" s="2">
         <v>45</v>
       </c>
-      <c r="G58" s="5" t="s">
+      <c r="G58" s="7" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>30</v>
       </c>
@@ -3075,17 +3046,17 @@
       <c r="D59" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E59" s="7">
+      <c r="E59" s="5">
         <v>2.1</v>
       </c>
       <c r="F59" s="2">
         <v>44</v>
       </c>
-      <c r="G59" s="5">
+      <c r="G59" s="7">
         <v>21</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>86</v>
       </c>
@@ -3098,17 +3069,17 @@
       <c r="D60" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E60" s="7">
+      <c r="E60" s="5">
         <v>4.03</v>
       </c>
       <c r="F60" s="2">
         <v>60.5</v>
       </c>
-      <c r="G60" s="5">
+      <c r="G60" s="7">
         <v>15</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>87</v>
       </c>
@@ -3121,17 +3092,17 @@
       <c r="D61" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E61" s="7">
+      <c r="E61" s="5">
         <v>1.5</v>
       </c>
       <c r="F61" s="2">
         <v>18</v>
       </c>
-      <c r="G61" s="5">
+      <c r="G61" s="7">
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>88</v>
       </c>
@@ -3144,17 +3115,17 @@
       <c r="D62" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E62" s="7">
+      <c r="E62" s="5">
         <v>1.5</v>
       </c>
       <c r="F62" s="2">
         <v>18</v>
       </c>
-      <c r="G62" s="5">
+      <c r="G62" s="7">
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>89</v>
       </c>
@@ -3167,17 +3138,17 @@
       <c r="D63" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E63" s="7">
+      <c r="E63" s="5">
         <v>1.5</v>
       </c>
       <c r="F63" s="2">
         <v>18</v>
       </c>
-      <c r="G63" s="5">
+      <c r="G63" s="7">
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>90</v>
       </c>
@@ -3190,13 +3161,13 @@
       <c r="D64" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E64" s="7">
+      <c r="E64" s="5">
         <v>1.5</v>
       </c>
       <c r="F64" s="2">
         <v>18</v>
       </c>
-      <c r="G64" s="5">
+      <c r="G64" s="7">
         <v>12</v>
       </c>
     </row>
@@ -3213,13 +3184,13 @@
       <c r="D65" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E65" s="7">
+      <c r="E65" s="5">
         <v>21</v>
       </c>
-      <c r="F65" s="7">
+      <c r="F65" s="5">
         <v>21</v>
       </c>
-      <c r="G65" s="5">
+      <c r="G65" s="7">
         <v>1</v>
       </c>
     </row>
@@ -3236,13 +3207,13 @@
       <c r="D66" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E66" s="7">
+      <c r="E66" s="5">
         <v>24.9</v>
       </c>
-      <c r="F66" s="7">
+      <c r="F66" s="5">
         <v>24.9</v>
       </c>
-      <c r="G66" s="5">
+      <c r="G66" s="7">
         <v>1</v>
       </c>
     </row>
@@ -3259,13 +3230,13 @@
       <c r="D67" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E67" s="7">
+      <c r="E67" s="5">
         <v>21</v>
       </c>
-      <c r="F67" s="7">
+      <c r="F67" s="5">
         <v>21</v>
       </c>
-      <c r="G67" s="5">
+      <c r="G67" s="7">
         <v>1</v>
       </c>
     </row>
@@ -3282,13 +3253,13 @@
       <c r="D68" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E68" s="7">
+      <c r="E68" s="5">
         <v>21</v>
       </c>
-      <c r="F68" s="7">
+      <c r="F68" s="5">
         <v>21</v>
       </c>
-      <c r="G68" s="5">
+      <c r="G68" s="7">
         <v>1</v>
       </c>
     </row>
@@ -3305,13 +3276,13 @@
       <c r="D69" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E69" s="7">
+      <c r="E69" s="5">
         <v>21</v>
       </c>
-      <c r="F69" s="7">
+      <c r="F69" s="5">
         <v>21</v>
       </c>
-      <c r="G69" s="5">
+      <c r="G69" s="7">
         <v>1</v>
       </c>
     </row>
@@ -3328,13 +3299,13 @@
       <c r="D70" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E70" s="7">
+      <c r="E70" s="5">
         <v>21</v>
       </c>
-      <c r="F70" s="7">
+      <c r="F70" s="5">
         <v>21</v>
       </c>
-      <c r="G70" s="5">
+      <c r="G70" s="7">
         <v>1</v>
       </c>
     </row>
@@ -3351,13 +3322,13 @@
       <c r="D71" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E71" s="7">
+      <c r="E71" s="5">
         <v>21</v>
       </c>
-      <c r="F71" s="7">
+      <c r="F71" s="5">
         <v>21</v>
       </c>
-      <c r="G71" s="5">
+      <c r="G71" s="7">
         <v>1</v>
       </c>
     </row>
@@ -3374,13 +3345,13 @@
       <c r="D72" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E72" s="7">
+      <c r="E72" s="5">
         <v>21</v>
       </c>
-      <c r="F72" s="7">
+      <c r="F72" s="5">
         <v>21</v>
       </c>
-      <c r="G72" s="5">
+      <c r="G72" s="7">
         <v>1</v>
       </c>
     </row>
@@ -3397,13 +3368,13 @@
       <c r="D73" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E73" s="7">
+      <c r="E73" s="5">
         <v>21</v>
       </c>
-      <c r="F73" s="7">
+      <c r="F73" s="5">
         <v>21</v>
       </c>
-      <c r="G73" s="5">
+      <c r="G73" s="7">
         <v>1</v>
       </c>
     </row>
@@ -3420,13 +3391,13 @@
       <c r="D74" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E74" s="7">
+      <c r="E74" s="5">
         <v>21</v>
       </c>
-      <c r="F74" s="7">
+      <c r="F74" s="5">
         <v>21</v>
       </c>
-      <c r="G74" s="5">
+      <c r="G74" s="7">
         <v>1</v>
       </c>
     </row>
@@ -3627,13 +3598,13 @@
       <c r="D83" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E83" s="7">
+      <c r="E83" s="5">
         <v>0.93</v>
       </c>
       <c r="F83" s="2">
         <v>21.5</v>
       </c>
-      <c r="G83" s="5">
+      <c r="G83" s="7">
         <v>23</v>
       </c>
     </row>
@@ -3650,13 +3621,13 @@
       <c r="D84" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E84" s="7">
+      <c r="E84" s="5">
         <v>0.43</v>
       </c>
       <c r="F84" s="2">
         <v>21.5</v>
       </c>
-      <c r="G84" s="5">
+      <c r="G84" s="7">
         <v>50</v>
       </c>
     </row>
@@ -3673,13 +3644,13 @@
       <c r="D85" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E85" s="7">
+      <c r="E85" s="5">
         <v>2.36</v>
       </c>
       <c r="F85" s="2">
         <v>47.14</v>
       </c>
-      <c r="G85" s="5">
+      <c r="G85" s="7">
         <v>20</v>
       </c>
     </row>
@@ -3696,13 +3667,13 @@
       <c r="D86" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E86" s="7">
+      <c r="E86" s="5">
         <v>21</v>
       </c>
       <c r="F86" s="2">
         <v>21</v>
       </c>
-      <c r="G86" s="5">
+      <c r="G86" s="7">
         <v>1</v>
       </c>
     </row>
@@ -3719,13 +3690,13 @@
       <c r="D87" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E87" s="7">
+      <c r="E87" s="5">
         <v>16</v>
       </c>
       <c r="F87" s="2">
         <v>16</v>
       </c>
-      <c r="G87" s="5" t="s">
+      <c r="G87" s="7" t="s">
         <v>177</v>
       </c>
     </row>
@@ -3742,13 +3713,13 @@
       <c r="D88" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E88" s="7">
+      <c r="E88" s="5">
         <v>2.2599999999999998</v>
       </c>
       <c r="F88" s="2">
         <v>54.29</v>
       </c>
-      <c r="G88" s="5">
+      <c r="G88" s="7">
         <v>24</v>
       </c>
     </row>
@@ -3765,13 +3736,13 @@
       <c r="D89" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E89" s="7">
+      <c r="E89" s="5">
         <v>5.29</v>
       </c>
       <c r="F89" s="2">
         <v>127</v>
       </c>
-      <c r="G89" s="5">
+      <c r="G89" s="7">
         <v>24</v>
       </c>
     </row>
@@ -3794,7 +3765,7 @@
       <c r="F90" s="2">
         <v>68.28</v>
       </c>
-      <c r="G90" s="5">
+      <c r="G90" s="7">
         <v>12</v>
       </c>
     </row>
@@ -3817,7 +3788,7 @@
       <c r="F91" s="2">
         <v>68.28</v>
       </c>
-      <c r="G91" s="5">
+      <c r="G91" s="7">
         <v>12</v>
       </c>
     </row>
@@ -3840,7 +3811,7 @@
       <c r="F92" s="2">
         <v>68.28</v>
       </c>
-      <c r="G92" s="5">
+      <c r="G92" s="7">
         <v>12</v>
       </c>
     </row>
@@ -3863,7 +3834,7 @@
       <c r="F93" s="2">
         <v>68.28</v>
       </c>
-      <c r="G93" s="5">
+      <c r="G93" s="7">
         <v>12</v>
       </c>
     </row>
@@ -3886,7 +3857,7 @@
       <c r="F94" s="2">
         <v>68.28</v>
       </c>
-      <c r="G94" s="5">
+      <c r="G94" s="7">
         <v>12</v>
       </c>
     </row>
@@ -3909,7 +3880,7 @@
       <c r="F95" s="2">
         <v>69.900000000000006</v>
       </c>
-      <c r="G95" s="5">
+      <c r="G95" s="7">
         <v>10</v>
       </c>
     </row>
@@ -3932,7 +3903,7 @@
       <c r="F96" s="2">
         <v>69.900000000000006</v>
       </c>
-      <c r="G96" s="5">
+      <c r="G96" s="7">
         <v>10</v>
       </c>
     </row>
@@ -3955,7 +3926,7 @@
       <c r="F97" s="2">
         <v>69.900000000000006</v>
       </c>
-      <c r="G97" s="5">
+      <c r="G97" s="7">
         <v>10</v>
       </c>
     </row>
@@ -3972,13 +3943,13 @@
       <c r="D98" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E98" s="7">
+      <c r="E98" s="5">
         <v>2.2599999999999998</v>
       </c>
       <c r="F98" s="2">
         <v>54.29</v>
       </c>
-      <c r="G98" s="5">
+      <c r="G98" s="7">
         <v>24</v>
       </c>
     </row>
@@ -4001,7 +3972,7 @@
       <c r="F99" s="2">
         <v>48.96</v>
       </c>
-      <c r="G99" s="5">
+      <c r="G99" s="7">
         <v>1</v>
       </c>
     </row>
@@ -4018,13 +3989,13 @@
       <c r="D100" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E100" s="7">
+      <c r="E100" s="5">
         <v>2.25</v>
       </c>
-      <c r="F100" s="6">
+      <c r="F100" s="4">
         <v>45</v>
       </c>
-      <c r="G100" s="4">
+      <c r="G100" s="6">
         <v>20</v>
       </c>
     </row>
@@ -4047,7 +4018,7 @@
       <c r="F101" s="2">
         <v>125</v>
       </c>
-      <c r="G101" s="5">
+      <c r="G101" s="7">
         <v>20</v>
       </c>
     </row>
@@ -4070,7 +4041,7 @@
       <c r="F102" s="2">
         <v>125</v>
       </c>
-      <c r="G102" s="5">
+      <c r="G102" s="7">
         <v>20</v>
       </c>
     </row>
@@ -4093,7 +4064,7 @@
       <c r="F103" s="2">
         <v>125</v>
       </c>
-      <c r="G103" s="5">
+      <c r="G103" s="7">
         <v>20</v>
       </c>
     </row>
@@ -4116,7 +4087,7 @@
       <c r="F104" s="2">
         <v>125</v>
       </c>
-      <c r="G104" s="5">
+      <c r="G104" s="7">
         <v>20</v>
       </c>
     </row>
@@ -4139,7 +4110,7 @@
       <c r="F105" s="2">
         <v>125</v>
       </c>
-      <c r="G105" s="5">
+      <c r="G105" s="7">
         <v>20</v>
       </c>
     </row>
@@ -4162,7 +4133,7 @@
       <c r="F106" s="2">
         <v>80</v>
       </c>
-      <c r="G106" s="5">
+      <c r="G106" s="7">
         <v>20</v>
       </c>
     </row>
@@ -4185,7 +4156,7 @@
       <c r="F107" s="2">
         <v>110</v>
       </c>
-      <c r="G107" s="5">
+      <c r="G107" s="7">
         <v>27</v>
       </c>
     </row>
@@ -4208,7 +4179,7 @@
       <c r="F108" s="2">
         <v>120</v>
       </c>
-      <c r="G108" s="5">
+      <c r="G108" s="7">
         <v>20</v>
       </c>
     </row>
@@ -4231,7 +4202,7 @@
       <c r="F109" s="2">
         <v>125</v>
       </c>
-      <c r="G109" s="5">
+      <c r="G109" s="7">
         <v>20</v>
       </c>
     </row>
@@ -4254,7 +4225,7 @@
       <c r="F110" s="2">
         <v>125</v>
       </c>
-      <c r="G110" s="5">
+      <c r="G110" s="7">
         <v>20</v>
       </c>
     </row>
@@ -4277,7 +4248,7 @@
       <c r="F111" s="2">
         <v>125</v>
       </c>
-      <c r="G111" s="5">
+      <c r="G111" s="7">
         <v>20</v>
       </c>
     </row>
@@ -4300,7 +4271,7 @@
       <c r="F112" s="2">
         <v>125</v>
       </c>
-      <c r="G112" s="5">
+      <c r="G112" s="7">
         <v>20</v>
       </c>
     </row>
@@ -4323,7 +4294,7 @@
       <c r="F113" s="2">
         <v>80</v>
       </c>
-      <c r="G113" s="5">
+      <c r="G113" s="7">
         <v>20</v>
       </c>
     </row>
@@ -4346,7 +4317,7 @@
       <c r="F114" s="2">
         <v>110</v>
       </c>
-      <c r="G114" s="5">
+      <c r="G114" s="7">
         <v>27</v>
       </c>
     </row>
@@ -4363,13 +4334,13 @@
       <c r="D115" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="E115" s="6">
+      <c r="E115" s="4">
         <v>2.33</v>
       </c>
       <c r="F115" s="2">
         <v>49</v>
       </c>
-      <c r="G115" s="5">
+      <c r="G115" s="7">
         <v>21</v>
       </c>
     </row>
@@ -4386,13 +4357,13 @@
       <c r="D116" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="E116" s="6">
+      <c r="E116" s="4">
         <v>2.33</v>
       </c>
       <c r="F116" s="2">
         <v>49</v>
       </c>
-      <c r="G116" s="5">
+      <c r="G116" s="7">
         <v>21</v>
       </c>
     </row>
@@ -4409,13 +4380,13 @@
       <c r="D117" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="E117" s="6">
+      <c r="E117" s="4">
         <v>2.33</v>
       </c>
       <c r="F117" s="2">
         <v>49</v>
       </c>
-      <c r="G117" s="5">
+      <c r="G117" s="7">
         <v>21</v>
       </c>
     </row>
@@ -4432,13 +4403,13 @@
       <c r="D118" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="E118" s="6">
+      <c r="E118" s="4">
         <v>4.4000000000000004</v>
       </c>
       <c r="F118" s="2">
         <v>88</v>
       </c>
-      <c r="G118" s="5">
+      <c r="G118" s="7">
         <v>20</v>
       </c>
     </row>
@@ -4455,13 +4426,13 @@
       <c r="D119" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="E119" s="6">
+      <c r="E119" s="4">
         <v>4.4000000000000004</v>
       </c>
       <c r="F119" s="2">
         <v>88</v>
       </c>
-      <c r="G119" s="5">
+      <c r="G119" s="7">
         <v>20</v>
       </c>
     </row>
@@ -4478,13 +4449,13 @@
       <c r="D120" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="E120" s="6">
+      <c r="E120" s="4">
         <v>5.65</v>
       </c>
       <c r="F120" s="2">
         <v>84.7</v>
       </c>
-      <c r="G120" s="5">
+      <c r="G120" s="7">
         <v>15</v>
       </c>
     </row>
@@ -4501,13 +4472,13 @@
       <c r="D121" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="E121" s="6">
+      <c r="E121" s="4">
         <v>5.65</v>
       </c>
       <c r="F121" s="2">
         <v>84.7</v>
       </c>
-      <c r="G121" s="5">
+      <c r="G121" s="7">
         <v>15</v>
       </c>
     </row>
@@ -4524,13 +4495,13 @@
       <c r="D122" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="E122" s="6">
+      <c r="E122" s="4">
         <v>5.65</v>
       </c>
       <c r="F122" s="2">
         <v>84.7</v>
       </c>
-      <c r="G122" s="5">
+      <c r="G122" s="7">
         <v>15</v>
       </c>
     </row>
@@ -4547,13 +4518,13 @@
       <c r="D123" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="E123" s="6">
+      <c r="E123" s="4">
         <v>2.17</v>
       </c>
       <c r="F123" s="2">
         <v>52</v>
       </c>
-      <c r="G123" s="5">
+      <c r="G123" s="7">
         <v>24</v>
       </c>
     </row>
@@ -4570,14 +4541,83 @@
       <c r="D124" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="E124" s="6">
+      <c r="E124" s="4">
         <v>2.17</v>
       </c>
       <c r="F124" s="2">
         <v>52</v>
       </c>
-      <c r="G124" s="5">
+      <c r="G124" s="7">
         <v>24</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C125" t="s">
+        <v>166</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E125" s="5">
+        <v>24.9</v>
+      </c>
+      <c r="F125" s="5">
+        <v>24.9</v>
+      </c>
+      <c r="G125" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C126" t="s">
+        <v>166</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E126" s="5">
+        <v>24.9</v>
+      </c>
+      <c r="F126" s="5">
+        <v>24.9</v>
+      </c>
+      <c r="G126" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C127" t="s">
+        <v>166</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E127" s="5">
+        <v>24.9</v>
+      </c>
+      <c r="F127" s="5">
+        <v>24.9</v>
+      </c>
+      <c r="G127" s="7">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1CFEFA7AFB5B64DF/bsbox/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{32DF9513-3448-4E5B-8499-1BE121EF9C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81087BF8-A02A-4CDE-86E3-F59700A74DB8}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{32DF9513-3448-4E5B-8499-1BE121EF9C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E65DF569-B256-4221-8B36-C36D9DE9097E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="261">
   <si>
     <t>categoria</t>
   </si>
@@ -803,6 +803,9 @@
   </si>
   <si>
     <t>01030613</t>
+  </si>
+  <si>
+    <t>DWK Doce Franchesco Cocada Cremosa Zero Açucar Pote 400g</t>
   </si>
 </sst>
 </file>
@@ -4582,7 +4585,7 @@
         <v>19</v>
       </c>
       <c r="C126" t="s">
-        <v>166</v>
+        <v>260</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>245</v>
@@ -4605,7 +4608,7 @@
         <v>19</v>
       </c>
       <c r="C127" t="s">
-        <v>166</v>
+        <v>260</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>20</v>

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1CFEFA7AFB5B64DF/bsbox/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="8_{32DF9513-3448-4E5B-8499-1BE121EF9C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E65DF569-B256-4221-8B36-C36D9DE9097E}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{32DF9513-3448-4E5B-8499-1BE121EF9C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E54A3444-1893-4FC0-ACFD-87C49987FD89}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="base_de_produtos" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">base_de_produtos!$A$1:$G$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">base_de_produtos!$A$1:$G$110</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="236">
   <si>
     <t>categoria</t>
   </si>
@@ -670,27 +670,12 @@
     <t>Doce de Leite com Coco No Ponto pote com 20 Unid</t>
   </si>
   <si>
-    <t>04050701</t>
-  </si>
-  <si>
     <t>Doce Pão de Mel 80g Pacote Misto 20 Unid</t>
   </si>
   <si>
-    <t>04050702</t>
-  </si>
-  <si>
     <t>Doce Pão de Mel 80g Doce de Leite 20 Unid</t>
   </si>
   <si>
-    <t>04050703</t>
-  </si>
-  <si>
-    <t>04050704</t>
-  </si>
-  <si>
-    <t>04050705</t>
-  </si>
-  <si>
     <t>Doce Pão de Mel 80g Brigadeiro 20 Unid</t>
   </si>
   <si>
@@ -700,21 +685,12 @@
     <t>Doce Pão de Mel 80g Beijinho 20 Unid</t>
   </si>
   <si>
-    <t>04050706</t>
-  </si>
-  <si>
     <t>Doce Alfajor 45g Doce de Leite 20 Unid</t>
   </si>
   <si>
-    <t>04050707</t>
-  </si>
-  <si>
     <t>Doce Trufa 40g Caixa Mista 27 Unid (Cereja, Beijinho, 2 Amores, Ninho)</t>
   </si>
   <si>
-    <t>LGM</t>
-  </si>
-  <si>
     <t>L4050701</t>
   </si>
   <si>
@@ -736,76 +712,25 @@
     <t>L4050702</t>
   </si>
   <si>
-    <t>PGM</t>
-  </si>
-  <si>
-    <t>DWK Cocada Amor de Coco Marrom pack com 20 Unid</t>
-  </si>
-  <si>
     <t>DWK Cocada Amor de Coco Branca pack com 20 Unid</t>
   </si>
   <si>
-    <t>DWK Cone Trufado Top Frutas Avelan Pack com 15 Unid</t>
-  </si>
-  <si>
-    <t>DWK Cone Trufado Top Frutas Tentação Pack com 15 Unid</t>
-  </si>
-  <si>
-    <t>DWK Cone Trufado Top frutas Leitinho Pack com 15 Unid</t>
-  </si>
-  <si>
-    <t>DWK Foudant  Pingado WK Leite (Bananinha) Pack com 24 Unid</t>
-  </si>
-  <si>
-    <t>DWK Foudant Pingado WK Leite com coco (Bananinha) Pack com 24 Unid</t>
-  </si>
-  <si>
-    <t>LWK</t>
-  </si>
-  <si>
-    <t>L1030543</t>
-  </si>
-  <si>
-    <t>L1030544</t>
-  </si>
-  <si>
-    <t>L1030508</t>
-  </si>
-  <si>
-    <t>L1030611</t>
-  </si>
-  <si>
-    <t>L1030527</t>
-  </si>
-  <si>
-    <t>L1030533</t>
-  </si>
-  <si>
-    <t>L1030530</t>
-  </si>
-  <si>
-    <t>L1030566</t>
-  </si>
-  <si>
-    <t>L1030609</t>
-  </si>
-  <si>
-    <t>L1030612</t>
-  </si>
-  <si>
     <t>DWK Beijo Chocolate Ouro de Minas Pote com 21 Unid</t>
   </si>
   <si>
-    <t>L1030552</t>
-  </si>
-  <si>
-    <t>L1030613</t>
-  </si>
-  <si>
     <t>01030613</t>
   </si>
   <si>
     <t>DWK Doce Franchesco Cocada Cremosa Zero Açucar Pote 400g</t>
+  </si>
+  <si>
+    <t>01030612</t>
+  </si>
+  <si>
+    <t>01030611</t>
+  </si>
+  <si>
+    <t>Gold Mel</t>
   </si>
 </sst>
 </file>
@@ -1684,7 +1609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}">
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -3004,10 +2929,10 @@
         <v>20</v>
       </c>
       <c r="E57" s="5">
-        <v>2.14</v>
+        <v>2.33</v>
       </c>
       <c r="F57" s="2">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G57" s="7" t="s">
         <v>85</v>
@@ -3027,10 +2952,10 @@
         <v>20</v>
       </c>
       <c r="E58" s="5">
-        <v>2.14</v>
+        <v>2.33</v>
       </c>
       <c r="F58" s="2">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G58" s="7" t="s">
         <v>85</v>
@@ -4004,16 +3929,16 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C101" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="E101" s="2">
         <v>6.25</v>
@@ -4027,16 +3952,16 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C102" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="E102" s="2">
         <v>6.25</v>
@@ -4050,16 +3975,16 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C103" t="s">
+        <v>217</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C103" t="s">
-        <v>222</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>229</v>
       </c>
       <c r="E103" s="2">
         <v>6.25</v>
@@ -4073,16 +3998,16 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C104" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="E104" s="2">
         <v>6.25</v>
@@ -4096,16 +4021,16 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C105" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="E105" s="2">
         <v>6.25</v>
@@ -4119,16 +4044,16 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C106" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="E106" s="2">
         <v>4</v>
@@ -4142,16 +4067,16 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C107" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="E107" s="2">
         <v>4.08</v>
@@ -4165,45 +4090,45 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C108" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="E108" s="2">
-        <v>6</v>
+        <v>20</v>
+      </c>
+      <c r="E108" s="4">
+        <v>2.33</v>
       </c>
       <c r="F108" s="2">
-        <v>120</v>
+        <v>49</v>
       </c>
       <c r="G108" s="7">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C109" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="E109" s="2">
-        <v>6</v>
+        <v>20</v>
+      </c>
+      <c r="E109" s="4">
+        <v>4.4000000000000004</v>
       </c>
       <c r="F109" s="2">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="G109" s="7">
         <v>20</v>
@@ -4211,419 +4136,29 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C110" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="E110" s="2">
-        <v>6</v>
-      </c>
-      <c r="F110" s="2">
-        <v>125</v>
+        <v>20</v>
+      </c>
+      <c r="E110" s="5">
+        <v>24.9</v>
+      </c>
+      <c r="F110" s="5">
+        <v>24.9</v>
       </c>
       <c r="G110" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A111" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C111" t="s">
-        <v>223</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="E111" s="2">
-        <v>6</v>
-      </c>
-      <c r="F111" s="2">
-        <v>125</v>
-      </c>
-      <c r="G111" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A112" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C112" t="s">
-        <v>224</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="E112" s="2">
-        <v>6</v>
-      </c>
-      <c r="F112" s="2">
-        <v>125</v>
-      </c>
-      <c r="G112" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C113" t="s">
-        <v>226</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="E113" s="2">
-        <v>4</v>
-      </c>
-      <c r="F113" s="2">
-        <v>80</v>
-      </c>
-      <c r="G113" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A114" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C114" t="s">
-        <v>228</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="E114" s="2">
-        <v>4.08</v>
-      </c>
-      <c r="F114" s="2">
-        <v>110</v>
-      </c>
-      <c r="G114" s="7">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A115" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C115" t="s">
-        <v>123</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E115" s="4">
-        <v>2.33</v>
-      </c>
-      <c r="F115" s="2">
-        <v>49</v>
-      </c>
-      <c r="G115" s="7">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A116" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C116" t="s">
-        <v>124</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E116" s="4">
-        <v>2.33</v>
-      </c>
-      <c r="F116" s="2">
-        <v>49</v>
-      </c>
-      <c r="G116" s="7">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A117" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C117" t="s">
-        <v>256</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E117" s="4">
-        <v>2.33</v>
-      </c>
-      <c r="F117" s="2">
-        <v>49</v>
-      </c>
-      <c r="G117" s="7">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A118" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C118" t="s">
-        <v>238</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E118" s="4">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F118" s="2">
-        <v>88</v>
-      </c>
-      <c r="G118" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A119" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C119" t="s">
-        <v>239</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E119" s="4">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F119" s="2">
-        <v>88</v>
-      </c>
-      <c r="G119" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A120" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C120" t="s">
-        <v>240</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E120" s="4">
-        <v>5.65</v>
-      </c>
-      <c r="F120" s="2">
-        <v>84.7</v>
-      </c>
-      <c r="G120" s="7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A121" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C121" t="s">
-        <v>241</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E121" s="4">
-        <v>5.65</v>
-      </c>
-      <c r="F121" s="2">
-        <v>84.7</v>
-      </c>
-      <c r="G121" s="7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A122" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C122" t="s">
-        <v>242</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E122" s="4">
-        <v>5.65</v>
-      </c>
-      <c r="F122" s="2">
-        <v>84.7</v>
-      </c>
-      <c r="G122" s="7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A123" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C123" t="s">
-        <v>243</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E123" s="4">
-        <v>2.17</v>
-      </c>
-      <c r="F123" s="2">
-        <v>52</v>
-      </c>
-      <c r="G123" s="7">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A124" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C124" t="s">
-        <v>244</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E124" s="4">
-        <v>2.17</v>
-      </c>
-      <c r="F124" s="2">
-        <v>52</v>
-      </c>
-      <c r="G124" s="7">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A125" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C125" t="s">
-        <v>166</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E125" s="5">
-        <v>24.9</v>
-      </c>
-      <c r="F125" s="5">
-        <v>24.9</v>
-      </c>
-      <c r="G125" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A126" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C126" t="s">
-        <v>260</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E126" s="5">
-        <v>24.9</v>
-      </c>
-      <c r="F126" s="5">
-        <v>24.9</v>
-      </c>
-      <c r="G126" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A127" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C127" t="s">
-        <v>260</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E127" s="5">
-        <v>24.9</v>
-      </c>
-      <c r="F127" s="5">
-        <v>24.9</v>
-      </c>
-      <c r="G127" s="7">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:G110" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1CFEFA7AFB5B64DF/bsbox/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1cfefa7afb5b64df/bsbox/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{32DF9513-3448-4E5B-8499-1BE121EF9C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E54A3444-1893-4FC0-ACFD-87C49987FD89}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="8_{32DF9513-3448-4E5B-8499-1BE121EF9C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BAB0C29-A633-4026-AA67-8F584CC78A8A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="237">
   <si>
     <t>categoria</t>
   </si>
@@ -731,6 +731,9 @@
   </si>
   <si>
     <t>Gold Mel</t>
+  </si>
+  <si>
+    <t>x Estoque x</t>
   </si>
 </sst>
 </file>
@@ -1609,7 +1612,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}">
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -4157,6 +4160,144 @@
         <v>1</v>
       </c>
     </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C111" t="s">
+        <v>215</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E111" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="F111" s="2">
+        <v>95</v>
+      </c>
+      <c r="G111" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C112" t="s">
+        <v>216</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E112" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="F112" s="2">
+        <v>4.75</v>
+      </c>
+      <c r="G112" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C113" t="s">
+        <v>217</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E113" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="F113" s="2">
+        <v>4.75</v>
+      </c>
+      <c r="G113" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C114" t="s">
+        <v>218</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E114" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="F114" s="2">
+        <v>4.75</v>
+      </c>
+      <c r="G114" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C115" t="s">
+        <v>219</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E115" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="F115" s="2">
+        <v>4.75</v>
+      </c>
+      <c r="G115" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C116" t="s">
+        <v>220</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E116" s="2">
+        <v>4</v>
+      </c>
+      <c r="F116" s="2">
+        <v>55</v>
+      </c>
+      <c r="G116" s="7">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G110" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1cfefa7afb5b64df/bsbox/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="8_{32DF9513-3448-4E5B-8499-1BE121EF9C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BAB0C29-A633-4026-AA67-8F584CC78A8A}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="8_{32DF9513-3448-4E5B-8499-1BE121EF9C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B91AAA6D-9012-4488-B93D-2F3707E3D0EC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -4174,7 +4174,7 @@
         <v>236</v>
       </c>
       <c r="E111" s="2">
-        <v>6.25</v>
+        <v>95</v>
       </c>
       <c r="F111" s="2">
         <v>95</v>
@@ -4197,10 +4197,10 @@
         <v>236</v>
       </c>
       <c r="E112" s="2">
-        <v>6.25</v>
+        <v>4.75</v>
       </c>
       <c r="F112" s="2">
-        <v>4.75</v>
+        <v>95</v>
       </c>
       <c r="G112" s="7">
         <v>20</v>
@@ -4220,10 +4220,10 @@
         <v>236</v>
       </c>
       <c r="E113" s="2">
-        <v>6.25</v>
+        <v>4.75</v>
       </c>
       <c r="F113" s="2">
-        <v>4.75</v>
+        <v>95</v>
       </c>
       <c r="G113" s="7">
         <v>20</v>
@@ -4243,10 +4243,10 @@
         <v>236</v>
       </c>
       <c r="E114" s="2">
-        <v>6.25</v>
+        <v>4.75</v>
       </c>
       <c r="F114" s="2">
-        <v>4.75</v>
+        <v>95</v>
       </c>
       <c r="G114" s="7">
         <v>20</v>
@@ -4266,10 +4266,10 @@
         <v>236</v>
       </c>
       <c r="E115" s="2">
-        <v>6.25</v>
+        <v>4.75</v>
       </c>
       <c r="F115" s="2">
-        <v>4.75</v>
+        <v>95</v>
       </c>
       <c r="G115" s="7">
         <v>20</v>
@@ -4289,7 +4289,7 @@
         <v>236</v>
       </c>
       <c r="E116" s="2">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F116" s="2">
         <v>55</v>

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1cfefa7afb5b64df/bsbox/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{32DF9513-3448-4E5B-8499-1BE121EF9C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B91AAA6D-9012-4488-B93D-2F3707E3D0EC}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="8_{32DF9513-3448-4E5B-8499-1BE121EF9C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE619F5A-160B-4E20-8D7D-C1CAFD21CEC4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="base_de_produtos" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">base_de_produtos!$A$1:$G$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">base_de_produtos!$A$1:$G$116</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="249">
   <si>
     <t>categoria</t>
   </si>
@@ -734,6 +734,42 @@
   </si>
   <si>
     <t>x Estoque x</t>
+  </si>
+  <si>
+    <t>4050701</t>
+  </si>
+  <si>
+    <t>4050702</t>
+  </si>
+  <si>
+    <t>4050703</t>
+  </si>
+  <si>
+    <t>4050704</t>
+  </si>
+  <si>
+    <t>4050705</t>
+  </si>
+  <si>
+    <t>4050706</t>
+  </si>
+  <si>
+    <t>Pão de Mel 80g Pacote Misto 20 Unid</t>
+  </si>
+  <si>
+    <t>Pão de Mel 80g Doce de Leite 20 Unid</t>
+  </si>
+  <si>
+    <t>Pão de Mel 80g Brigadeiro 20 Unid</t>
+  </si>
+  <si>
+    <t>Pão de Mel 80g Floresta Negra 20 Unid</t>
+  </si>
+  <si>
+    <t>Pão de Mel 80g Beijinho 20 Unid</t>
+  </si>
+  <si>
+    <t>Alfajor 45g Doce de Leite 20 Unid</t>
   </si>
 </sst>
 </file>
@@ -4162,13 +4198,13 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C111" t="s">
-        <v>215</v>
+        <v>243</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>236</v>
@@ -4185,13 +4221,13 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C112" t="s">
-        <v>216</v>
+        <v>244</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>236</v>
@@ -4208,13 +4244,13 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C113" t="s">
-        <v>217</v>
+        <v>245</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>236</v>
@@ -4231,13 +4267,13 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C114" t="s">
-        <v>218</v>
+        <v>246</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>236</v>
@@ -4254,13 +4290,13 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C115" t="s">
-        <v>219</v>
+        <v>247</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>236</v>
@@ -4277,13 +4313,13 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C116" t="s">
-        <v>220</v>
+        <v>248</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>236</v>
@@ -4299,7 +4335,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G110" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}"/>
+  <autoFilter ref="A1:G116" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1cfefa7afb5b64df/bsbox/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="8_{32DF9513-3448-4E5B-8499-1BE121EF9C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE619F5A-160B-4E20-8D7D-C1CAFD21CEC4}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="8_{32DF9513-3448-4E5B-8499-1BE121EF9C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48786AFD-AEE5-4FDC-AC8B-1A503BB40989}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="250">
   <si>
     <t>categoria</t>
   </si>
@@ -770,6 +770,9 @@
   </si>
   <si>
     <t>Alfajor 45g Doce de Leite 20 Unid</t>
+  </si>
+  <si>
+    <t>4050707</t>
   </si>
 </sst>
 </file>
@@ -1648,7 +1651,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}">
-  <dimension ref="A1:G116"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -1683,7 +1687,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>58</v>
       </c>
@@ -1706,7 +1710,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>59</v>
       </c>
@@ -1729,7 +1733,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>60</v>
       </c>
@@ -1752,7 +1756,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>61</v>
       </c>
@@ -1775,7 +1779,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>62</v>
       </c>
@@ -1798,7 +1802,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>63</v>
       </c>
@@ -1821,7 +1825,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>64</v>
       </c>
@@ -1844,7 +1848,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>65</v>
       </c>
@@ -1867,7 +1871,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>66</v>
       </c>
@@ -1890,7 +1894,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>67</v>
       </c>
@@ -1913,7 +1917,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>68</v>
       </c>
@@ -1937,7 +1941,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>71</v>
       </c>
@@ -1961,7 +1965,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>72</v>
       </c>
@@ -1985,7 +1989,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>75</v>
       </c>
@@ -2009,7 +2013,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>76</v>
       </c>
@@ -2033,7 +2037,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>78</v>
       </c>
@@ -2057,7 +2061,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
@@ -2080,7 +2084,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
@@ -2103,7 +2107,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
@@ -2126,7 +2130,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>24</v>
       </c>
@@ -2149,7 +2153,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
@@ -2172,7 +2176,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>26</v>
       </c>
@@ -2195,7 +2199,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>27</v>
       </c>
@@ -2218,7 +2222,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>28</v>
       </c>
@@ -2241,7 +2245,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>29</v>
       </c>
@@ -2264,7 +2268,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>47</v>
       </c>
@@ -2287,7 +2291,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>31</v>
       </c>
@@ -2310,7 +2314,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>32</v>
       </c>
@@ -2333,7 +2337,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>33</v>
       </c>
@@ -2356,7 +2360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>34</v>
       </c>
@@ -2379,7 +2383,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>35</v>
       </c>
@@ -2402,7 +2406,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>36</v>
       </c>
@@ -2425,7 +2429,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>37</v>
       </c>
@@ -2448,7 +2452,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>38</v>
       </c>
@@ -2471,7 +2475,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>39</v>
       </c>
@@ -2494,7 +2498,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>40</v>
       </c>
@@ -2517,7 +2521,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>41</v>
       </c>
@@ -2540,7 +2544,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>42</v>
       </c>
@@ -2563,7 +2567,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>43</v>
       </c>
@@ -2586,7 +2590,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>44</v>
       </c>
@@ -2609,7 +2613,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>45</v>
       </c>
@@ -2632,7 +2636,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>46</v>
       </c>
@@ -2655,7 +2659,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>48</v>
       </c>
@@ -2678,7 +2682,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>49</v>
       </c>
@@ -2701,7 +2705,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>50</v>
       </c>
@@ -2724,7 +2728,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>51</v>
       </c>
@@ -2747,7 +2751,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>52</v>
       </c>
@@ -2770,7 +2774,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>53</v>
       </c>
@@ -2793,7 +2797,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>54</v>
       </c>
@@ -2816,7 +2820,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>55</v>
       </c>
@@ -2839,7 +2843,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>56</v>
       </c>
@@ -2862,7 +2866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>57</v>
       </c>
@@ -2885,7 +2889,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>80</v>
       </c>
@@ -2908,7 +2912,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>81</v>
       </c>
@@ -2931,7 +2935,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>82</v>
       </c>
@@ -2954,7 +2958,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>83</v>
       </c>
@@ -2977,7 +2981,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>84</v>
       </c>
@@ -3000,7 +3004,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>30</v>
       </c>
@@ -3023,7 +3027,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>86</v>
       </c>
@@ -3046,7 +3050,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>87</v>
       </c>
@@ -3069,7 +3073,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>88</v>
       </c>
@@ -3092,7 +3096,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>89</v>
       </c>
@@ -3115,7 +3119,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>90</v>
       </c>
@@ -3138,7 +3142,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>92</v>
       </c>
@@ -3161,7 +3165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>130</v>
       </c>
@@ -3184,7 +3188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>131</v>
       </c>
@@ -3207,7 +3211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>132</v>
       </c>
@@ -3230,7 +3234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>133</v>
       </c>
@@ -3253,7 +3257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>134</v>
       </c>
@@ -3276,7 +3280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>135</v>
       </c>
@@ -3299,7 +3303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>136</v>
       </c>
@@ -3322,7 +3326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>137</v>
       </c>
@@ -3345,7 +3349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>138</v>
       </c>
@@ -3368,7 +3372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>139</v>
       </c>
@@ -3391,7 +3395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>142</v>
       </c>
@@ -3414,7 +3418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>146</v>
       </c>
@@ -3437,7 +3441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>148</v>
       </c>
@@ -3460,7 +3464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>150</v>
       </c>
@@ -3483,7 +3487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>151</v>
       </c>
@@ -3506,7 +3510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>154</v>
       </c>
@@ -3529,7 +3533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>156</v>
       </c>
@@ -3552,7 +3556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>158</v>
       </c>
@@ -3575,7 +3579,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>159</v>
       </c>
@@ -3598,7 +3602,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>160</v>
       </c>
@@ -3621,7 +3625,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>162</v>
       </c>
@@ -3644,7 +3648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>178</v>
       </c>
@@ -3667,7 +3671,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>179</v>
       </c>
@@ -3690,7 +3694,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>180</v>
       </c>
@@ -3713,7 +3717,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>182</v>
       </c>
@@ -3736,7 +3740,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>190</v>
       </c>
@@ -3759,7 +3763,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>191</v>
       </c>
@@ -3782,7 +3786,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>192</v>
       </c>
@@ -3805,7 +3809,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>193</v>
       </c>
@@ -3828,7 +3832,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>194</v>
       </c>
@@ -3851,7 +3855,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>197</v>
       </c>
@@ -3874,7 +3878,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>198</v>
       </c>
@@ -3897,7 +3901,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>199</v>
       </c>
@@ -3920,7 +3924,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>212</v>
       </c>
@@ -3943,7 +3947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>213</v>
       </c>
@@ -4127,7 +4131,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>233</v>
       </c>
@@ -4150,7 +4154,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>234</v>
       </c>
@@ -4173,7 +4177,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>231</v>
       </c>
@@ -4236,7 +4240,7 @@
         <v>4.75</v>
       </c>
       <c r="F112" s="2">
-        <v>95</v>
+        <v>4.75</v>
       </c>
       <c r="G112" s="7">
         <v>20</v>
@@ -4259,7 +4263,7 @@
         <v>4.75</v>
       </c>
       <c r="F113" s="2">
-        <v>95</v>
+        <v>4.75</v>
       </c>
       <c r="G113" s="7">
         <v>20</v>
@@ -4282,7 +4286,7 @@
         <v>4.75</v>
       </c>
       <c r="F114" s="2">
-        <v>95</v>
+        <v>4.75</v>
       </c>
       <c r="G114" s="7">
         <v>20</v>
@@ -4305,7 +4309,7 @@
         <v>4.75</v>
       </c>
       <c r="F115" s="2">
-        <v>95</v>
+        <v>4.75</v>
       </c>
       <c r="G115" s="7">
         <v>20</v>
@@ -4334,8 +4338,38 @@
         <v>20</v>
       </c>
     </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C117" t="s">
+        <v>221</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E117" s="2">
+        <v>110</v>
+      </c>
+      <c r="F117" s="2">
+        <v>110</v>
+      </c>
+      <c r="G117" s="7">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G116" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}"/>
+  <autoFilter ref="A1:G116" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Gold Mel"/>
+        <filter val="x Estoque x"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1cfefa7afb5b64df/bsbox/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="8_{32DF9513-3448-4E5B-8499-1BE121EF9C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48786AFD-AEE5-4FDC-AC8B-1A503BB40989}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="8_{32DF9513-3448-4E5B-8499-1BE121EF9C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62634D83-9EBE-4100-A878-0BD9B84CBC5B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="base_de_produtos" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">base_de_produtos!$A$1:$G$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">base_de_produtos!$A$1:$G$117</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -1651,7 +1651,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G117"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1687,7 +1686,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>58</v>
       </c>
@@ -1710,7 +1709,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>59</v>
       </c>
@@ -1733,7 +1732,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>60</v>
       </c>
@@ -1756,7 +1755,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>61</v>
       </c>
@@ -1779,7 +1778,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>62</v>
       </c>
@@ -1802,7 +1801,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>63</v>
       </c>
@@ -1825,7 +1824,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>64</v>
       </c>
@@ -1848,7 +1847,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>65</v>
       </c>
@@ -1871,7 +1870,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>66</v>
       </c>
@@ -1894,7 +1893,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>67</v>
       </c>
@@ -1917,7 +1916,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>68</v>
       </c>
@@ -1941,7 +1940,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>71</v>
       </c>
@@ -1965,7 +1964,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>72</v>
       </c>
@@ -1989,7 +1988,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>75</v>
       </c>
@@ -2013,7 +2012,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>76</v>
       </c>
@@ -2037,7 +2036,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>78</v>
       </c>
@@ -2061,7 +2060,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
@@ -2084,7 +2083,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
@@ -2107,7 +2106,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
@@ -2130,7 +2129,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>24</v>
       </c>
@@ -2153,7 +2152,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
@@ -2176,7 +2175,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>26</v>
       </c>
@@ -2199,7 +2198,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>27</v>
       </c>
@@ -2222,7 +2221,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>28</v>
       </c>
@@ -2245,7 +2244,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>29</v>
       </c>
@@ -2268,7 +2267,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>47</v>
       </c>
@@ -2291,7 +2290,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>31</v>
       </c>
@@ -2314,7 +2313,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>32</v>
       </c>
@@ -2337,7 +2336,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>33</v>
       </c>
@@ -2360,7 +2359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>34</v>
       </c>
@@ -2383,7 +2382,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>35</v>
       </c>
@@ -2406,7 +2405,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>36</v>
       </c>
@@ -2429,7 +2428,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>37</v>
       </c>
@@ -2452,7 +2451,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>38</v>
       </c>
@@ -2475,7 +2474,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>39</v>
       </c>
@@ -2498,7 +2497,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>40</v>
       </c>
@@ -2521,7 +2520,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>41</v>
       </c>
@@ -2544,7 +2543,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>42</v>
       </c>
@@ -2567,7 +2566,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>43</v>
       </c>
@@ -2590,7 +2589,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>44</v>
       </c>
@@ -2613,7 +2612,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>45</v>
       </c>
@@ -2636,7 +2635,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>46</v>
       </c>
@@ -2659,7 +2658,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>48</v>
       </c>
@@ -2682,7 +2681,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>49</v>
       </c>
@@ -2705,7 +2704,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>50</v>
       </c>
@@ -2728,7 +2727,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>51</v>
       </c>
@@ -2751,7 +2750,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>52</v>
       </c>
@@ -2774,7 +2773,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>53</v>
       </c>
@@ -2797,7 +2796,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>54</v>
       </c>
@@ -2820,7 +2819,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>55</v>
       </c>
@@ -2843,7 +2842,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>56</v>
       </c>
@@ -2866,7 +2865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>57</v>
       </c>
@@ -2889,7 +2888,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>80</v>
       </c>
@@ -2912,7 +2911,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>81</v>
       </c>
@@ -2935,7 +2934,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>82</v>
       </c>
@@ -2958,7 +2957,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>83</v>
       </c>
@@ -2981,7 +2980,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>84</v>
       </c>
@@ -3004,7 +3003,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>30</v>
       </c>
@@ -3027,7 +3026,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>86</v>
       </c>
@@ -3050,7 +3049,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>87</v>
       </c>
@@ -3073,7 +3072,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>88</v>
       </c>
@@ -3096,7 +3095,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>89</v>
       </c>
@@ -3119,7 +3118,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>90</v>
       </c>
@@ -3142,7 +3141,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>92</v>
       </c>
@@ -3165,7 +3164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>130</v>
       </c>
@@ -3188,7 +3187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>131</v>
       </c>
@@ -3211,7 +3210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>132</v>
       </c>
@@ -3234,7 +3233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>133</v>
       </c>
@@ -3257,7 +3256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>134</v>
       </c>
@@ -3280,7 +3279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>135</v>
       </c>
@@ -3303,7 +3302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>136</v>
       </c>
@@ -3326,7 +3325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>137</v>
       </c>
@@ -3349,7 +3348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>138</v>
       </c>
@@ -3372,7 +3371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>139</v>
       </c>
@@ -3395,7 +3394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>142</v>
       </c>
@@ -3418,7 +3417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>146</v>
       </c>
@@ -3441,7 +3440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>148</v>
       </c>
@@ -3464,7 +3463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>150</v>
       </c>
@@ -3487,7 +3486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>151</v>
       </c>
@@ -3510,7 +3509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>154</v>
       </c>
@@ -3533,7 +3532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>156</v>
       </c>
@@ -3556,7 +3555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>158</v>
       </c>
@@ -3579,7 +3578,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>159</v>
       </c>
@@ -3602,7 +3601,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>160</v>
       </c>
@@ -3625,7 +3624,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>162</v>
       </c>
@@ -3648,7 +3647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>178</v>
       </c>
@@ -3671,7 +3670,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>179</v>
       </c>
@@ -3694,7 +3693,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>180</v>
       </c>
@@ -3717,7 +3716,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>182</v>
       </c>
@@ -3740,7 +3739,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>190</v>
       </c>
@@ -3763,7 +3762,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>191</v>
       </c>
@@ -3786,7 +3785,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>192</v>
       </c>
@@ -3809,7 +3808,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>193</v>
       </c>
@@ -3832,7 +3831,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>194</v>
       </c>
@@ -3855,7 +3854,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>197</v>
       </c>
@@ -3878,7 +3877,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>198</v>
       </c>
@@ -3901,7 +3900,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>199</v>
       </c>
@@ -3924,7 +3923,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>212</v>
       </c>
@@ -3947,7 +3946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>213</v>
       </c>
@@ -4131,7 +4130,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>233</v>
       </c>
@@ -4154,7 +4153,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>234</v>
       </c>
@@ -4177,7 +4176,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>231</v>
       </c>
@@ -4362,14 +4361,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G116" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="Gold Mel"/>
-        <filter val="x Estoque x"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:G117" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1cfefa7afb5b64df/bsbox/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="8_{32DF9513-3448-4E5B-8499-1BE121EF9C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62634D83-9EBE-4100-A878-0BD9B84CBC5B}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="8_{32DF9513-3448-4E5B-8499-1BE121EF9C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE3A9856-1C1D-485C-88E5-F907C4CA4280}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -4351,10 +4351,10 @@
         <v>236</v>
       </c>
       <c r="E117" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="F117" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="G117" s="7">
         <v>27</v>
